--- a/output/version3/test/25-15/MARL/IL/RL-RL/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/IL/RL-RL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="C2" t="n">
-        <v>1149</v>
+        <v>1140</v>
       </c>
       <c r="D2" t="n">
-        <v>1107</v>
+        <v>1261</v>
       </c>
       <c r="E2" t="n">
-        <v>1134</v>
+        <v>1045</v>
       </c>
       <c r="F2" t="n">
-        <v>1268</v>
+        <v>1194</v>
       </c>
       <c r="G2" t="n">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="H2" t="n">
-        <v>1192</v>
+        <v>1183</v>
       </c>
       <c r="I2" t="n">
-        <v>1233</v>
+        <v>1169</v>
       </c>
       <c r="J2" t="n">
-        <v>1063</v>
+        <v>1168</v>
       </c>
       <c r="K2" t="n">
-        <v>1166</v>
+        <v>1157</v>
       </c>
       <c r="L2" t="n">
-        <v>1166.6</v>
+        <v>1168.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1032</v>
+        <v>1312</v>
       </c>
       <c r="C3" t="n">
-        <v>958</v>
+        <v>1038</v>
       </c>
       <c r="D3" t="n">
-        <v>997</v>
+        <v>1058</v>
       </c>
       <c r="E3" t="n">
-        <v>966</v>
+        <v>1051</v>
       </c>
       <c r="F3" t="n">
-        <v>1113</v>
+        <v>1088</v>
       </c>
       <c r="G3" t="n">
-        <v>965</v>
+        <v>1064</v>
       </c>
       <c r="H3" t="n">
-        <v>1037</v>
+        <v>1121</v>
       </c>
       <c r="I3" t="n">
-        <v>1123</v>
+        <v>1191</v>
       </c>
       <c r="J3" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="K3" t="n">
-        <v>1250</v>
+        <v>1094</v>
       </c>
       <c r="L3" t="n">
-        <v>1056.8</v>
+        <v>1114.3</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1025</v>
+        <v>1282</v>
       </c>
       <c r="C4" t="n">
-        <v>1091</v>
+        <v>1164</v>
       </c>
       <c r="D4" t="n">
-        <v>1128</v>
+        <v>1027</v>
       </c>
       <c r="E4" t="n">
-        <v>1021</v>
+        <v>1265</v>
       </c>
       <c r="F4" t="n">
-        <v>1253</v>
+        <v>1046</v>
       </c>
       <c r="G4" t="n">
-        <v>1073</v>
+        <v>944</v>
       </c>
       <c r="H4" t="n">
-        <v>1130</v>
+        <v>1190</v>
       </c>
       <c r="I4" t="n">
-        <v>1189</v>
+        <v>1095</v>
       </c>
       <c r="J4" t="n">
-        <v>1112</v>
+        <v>1206</v>
       </c>
       <c r="K4" t="n">
-        <v>1337</v>
+        <v>1026</v>
       </c>
       <c r="L4" t="n">
-        <v>1135.9</v>
+        <v>1124.5</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="C5" t="n">
-        <v>994</v>
+        <v>939</v>
       </c>
       <c r="D5" t="n">
-        <v>947</v>
+        <v>1051</v>
       </c>
       <c r="E5" t="n">
-        <v>964</v>
+        <v>1023</v>
       </c>
       <c r="F5" t="n">
-        <v>1102</v>
+        <v>987</v>
       </c>
       <c r="G5" t="n">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="H5" t="n">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="I5" t="n">
-        <v>1040</v>
+        <v>982</v>
       </c>
       <c r="J5" t="n">
-        <v>989</v>
+        <v>1186</v>
       </c>
       <c r="K5" t="n">
-        <v>1018</v>
+        <v>980</v>
       </c>
       <c r="L5" t="n">
-        <v>1006.5</v>
+        <v>1015.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1142</v>
+        <v>1262</v>
       </c>
       <c r="C6" t="n">
-        <v>1055</v>
+        <v>1216</v>
       </c>
       <c r="D6" t="n">
-        <v>1096</v>
+        <v>1146</v>
       </c>
       <c r="E6" t="n">
-        <v>1070</v>
+        <v>1008</v>
       </c>
       <c r="F6" t="n">
-        <v>1102</v>
+        <v>1033</v>
       </c>
       <c r="G6" t="n">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="H6" t="n">
-        <v>1149</v>
+        <v>1314</v>
       </c>
       <c r="I6" t="n">
-        <v>1297</v>
+        <v>1092</v>
       </c>
       <c r="J6" t="n">
-        <v>1229</v>
+        <v>1073</v>
       </c>
       <c r="K6" t="n">
-        <v>1058</v>
+        <v>1178</v>
       </c>
       <c r="L6" t="n">
-        <v>1135.6</v>
+        <v>1149.7</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1066</v>
+        <v>998</v>
       </c>
       <c r="C7" t="n">
-        <v>1119</v>
+        <v>1006</v>
       </c>
       <c r="D7" t="n">
-        <v>1042</v>
+        <v>1012</v>
       </c>
       <c r="E7" t="n">
-        <v>1093</v>
+        <v>1163</v>
       </c>
       <c r="F7" t="n">
-        <v>1125</v>
+        <v>1009</v>
       </c>
       <c r="G7" t="n">
-        <v>967</v>
+        <v>1023</v>
       </c>
       <c r="H7" t="n">
-        <v>1090</v>
+        <v>952</v>
       </c>
       <c r="I7" t="n">
-        <v>955</v>
+        <v>1023</v>
       </c>
       <c r="J7" t="n">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="K7" t="n">
-        <v>1181</v>
+        <v>987</v>
       </c>
       <c r="L7" t="n">
-        <v>1062.1</v>
+        <v>1014.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1043</v>
+        <v>1016</v>
       </c>
       <c r="C8" t="n">
-        <v>1103</v>
+        <v>1089</v>
       </c>
       <c r="D8" t="n">
-        <v>1260</v>
+        <v>1075</v>
       </c>
       <c r="E8" t="n">
-        <v>1099</v>
+        <v>1012</v>
       </c>
       <c r="F8" t="n">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="G8" t="n">
-        <v>1223</v>
+        <v>982</v>
       </c>
       <c r="H8" t="n">
-        <v>1081</v>
+        <v>897</v>
       </c>
       <c r="I8" t="n">
-        <v>1251</v>
+        <v>1031</v>
       </c>
       <c r="J8" t="n">
-        <v>1039</v>
+        <v>961</v>
       </c>
       <c r="K8" t="n">
-        <v>1116</v>
+        <v>1098</v>
       </c>
       <c r="L8" t="n">
-        <v>1137.3</v>
+        <v>1031.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>941</v>
+        <v>1043</v>
       </c>
       <c r="C9" t="n">
-        <v>966</v>
+        <v>881</v>
       </c>
       <c r="D9" t="n">
-        <v>942</v>
+        <v>910</v>
       </c>
       <c r="E9" t="n">
-        <v>1000</v>
+        <v>957</v>
       </c>
       <c r="F9" t="n">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="G9" t="n">
-        <v>1036</v>
+        <v>1083</v>
       </c>
       <c r="H9" t="n">
-        <v>1015</v>
+        <v>1034</v>
       </c>
       <c r="I9" t="n">
-        <v>1043</v>
+        <v>939</v>
       </c>
       <c r="J9" t="n">
-        <v>935</v>
+        <v>1073</v>
       </c>
       <c r="K9" t="n">
-        <v>1035</v>
+        <v>995</v>
       </c>
       <c r="L9" t="n">
-        <v>979.8</v>
+        <v>980.8</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>996</v>
+        <v>1052</v>
       </c>
       <c r="C10" t="n">
-        <v>1177</v>
+        <v>933</v>
       </c>
       <c r="D10" t="n">
-        <v>1067</v>
+        <v>1100</v>
       </c>
       <c r="E10" t="n">
-        <v>1105</v>
+        <v>1053</v>
       </c>
       <c r="F10" t="n">
-        <v>987</v>
+        <v>1069</v>
       </c>
       <c r="G10" t="n">
-        <v>1238</v>
+        <v>1107</v>
       </c>
       <c r="H10" t="n">
-        <v>1106</v>
+        <v>1219</v>
       </c>
       <c r="I10" t="n">
-        <v>1019</v>
+        <v>1100</v>
       </c>
       <c r="J10" t="n">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="K10" t="n">
-        <v>1062</v>
+        <v>1097</v>
       </c>
       <c r="L10" t="n">
-        <v>1082.1</v>
+        <v>1079.5</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>984</v>
+        <v>1199</v>
       </c>
       <c r="C11" t="n">
-        <v>1198</v>
+        <v>1163</v>
       </c>
       <c r="D11" t="n">
-        <v>1062</v>
+        <v>1095</v>
       </c>
       <c r="E11" t="n">
+        <v>1220</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1194</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1038</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1196</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1126</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1022</v>
+      </c>
+      <c r="K11" t="n">
         <v>1088</v>
       </c>
-      <c r="F11" t="n">
-        <v>1128</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1124</v>
-      </c>
-      <c r="I11" t="n">
-        <v>995</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1121</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1032</v>
-      </c>
       <c r="L11" t="n">
-        <v>1082.4</v>
+        <v>1134.1</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1245</v>
+        <v>998</v>
       </c>
       <c r="C12" t="n">
-        <v>1079</v>
+        <v>1190</v>
       </c>
       <c r="D12" t="n">
-        <v>1127</v>
+        <v>1092</v>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>1148</v>
       </c>
       <c r="F12" t="n">
-        <v>1153</v>
+        <v>1230</v>
       </c>
       <c r="G12" t="n">
-        <v>1069</v>
+        <v>1020</v>
       </c>
       <c r="H12" t="n">
-        <v>1028</v>
+        <v>1054</v>
       </c>
       <c r="I12" t="n">
-        <v>1272</v>
+        <v>1095</v>
       </c>
       <c r="J12" t="n">
         <v>1197</v>
       </c>
       <c r="K12" t="n">
-        <v>1133</v>
+        <v>1152</v>
       </c>
       <c r="L12" t="n">
-        <v>1150.8</v>
+        <v>1117.6</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1436</v>
+        <v>1120</v>
       </c>
       <c r="C13" t="n">
-        <v>1323</v>
+        <v>1119</v>
       </c>
       <c r="D13" t="n">
-        <v>1244</v>
+        <v>1347</v>
       </c>
       <c r="E13" t="n">
-        <v>1280</v>
+        <v>1220</v>
       </c>
       <c r="F13" t="n">
-        <v>1335</v>
+        <v>1426</v>
       </c>
       <c r="G13" t="n">
-        <v>1206</v>
+        <v>1314</v>
       </c>
       <c r="H13" t="n">
-        <v>1170</v>
+        <v>1203</v>
       </c>
       <c r="I13" t="n">
-        <v>1398</v>
+        <v>1333</v>
       </c>
       <c r="J13" t="n">
-        <v>1269</v>
+        <v>1173</v>
       </c>
       <c r="K13" t="n">
-        <v>1130</v>
+        <v>1255</v>
       </c>
       <c r="L13" t="n">
-        <v>1279.1</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>911</v>
+        <v>1059</v>
       </c>
       <c r="C14" t="n">
-        <v>1024</v>
+        <v>972</v>
       </c>
       <c r="D14" t="n">
-        <v>976</v>
+        <v>1014</v>
       </c>
       <c r="E14" t="n">
-        <v>1145</v>
+        <v>1047</v>
       </c>
       <c r="F14" t="n">
-        <v>993</v>
+        <v>1032</v>
       </c>
       <c r="G14" t="n">
+        <v>1048</v>
+      </c>
+      <c r="H14" t="n">
+        <v>977</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1041</v>
+      </c>
+      <c r="J14" t="n">
         <v>1006</v>
       </c>
-      <c r="H14" t="n">
-        <v>1285</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1195</v>
-      </c>
-      <c r="J14" t="n">
-        <v>996</v>
-      </c>
       <c r="K14" t="n">
-        <v>989</v>
+        <v>968</v>
       </c>
       <c r="L14" t="n">
-        <v>1052</v>
+        <v>1016.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1395</v>
+        <v>1194</v>
       </c>
       <c r="C15" t="n">
-        <v>1024</v>
+        <v>1059</v>
       </c>
       <c r="D15" t="n">
-        <v>1139</v>
+        <v>1087</v>
       </c>
       <c r="E15" t="n">
-        <v>1091</v>
+        <v>1060</v>
       </c>
       <c r="F15" t="n">
-        <v>1017</v>
+        <v>1109</v>
       </c>
       <c r="G15" t="n">
-        <v>960</v>
+        <v>1146</v>
       </c>
       <c r="H15" t="n">
-        <v>980</v>
+        <v>1117</v>
       </c>
       <c r="I15" t="n">
-        <v>950</v>
+        <v>1115</v>
       </c>
       <c r="J15" t="n">
-        <v>1044</v>
+        <v>983</v>
       </c>
       <c r="K15" t="n">
-        <v>1127</v>
+        <v>1007</v>
       </c>
       <c r="L15" t="n">
-        <v>1072.7</v>
+        <v>1087.7</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1196</v>
+        <v>892</v>
       </c>
       <c r="C16" t="n">
-        <v>1129</v>
+        <v>1027</v>
       </c>
       <c r="D16" t="n">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="E16" t="n">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="F16" t="n">
-        <v>971</v>
+        <v>1030</v>
       </c>
       <c r="G16" t="n">
-        <v>1006</v>
+        <v>1112</v>
       </c>
       <c r="H16" t="n">
-        <v>1073</v>
+        <v>1002</v>
       </c>
       <c r="I16" t="n">
-        <v>957</v>
+        <v>1147</v>
       </c>
       <c r="J16" t="n">
-        <v>1174</v>
+        <v>1008</v>
       </c>
       <c r="K16" t="n">
-        <v>1104</v>
+        <v>1133</v>
       </c>
       <c r="L16" t="n">
-        <v>1072.7</v>
+        <v>1048.6</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1097</v>
+        <v>1219</v>
       </c>
       <c r="C17" t="n">
-        <v>1108</v>
+        <v>1044</v>
       </c>
       <c r="D17" t="n">
-        <v>1233</v>
+        <v>1054</v>
       </c>
       <c r="E17" t="n">
-        <v>1309</v>
+        <v>1086</v>
       </c>
       <c r="F17" t="n">
-        <v>1096</v>
+        <v>1125</v>
       </c>
       <c r="G17" t="n">
-        <v>1123</v>
+        <v>1203</v>
       </c>
       <c r="H17" t="n">
-        <v>1133</v>
+        <v>1104</v>
       </c>
       <c r="I17" t="n">
-        <v>1042</v>
+        <v>1182</v>
       </c>
       <c r="J17" t="n">
-        <v>1121</v>
+        <v>1189</v>
       </c>
       <c r="K17" t="n">
-        <v>1226</v>
+        <v>1177</v>
       </c>
       <c r="L17" t="n">
-        <v>1148.8</v>
+        <v>1138.3</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>976</v>
+        <v>1107</v>
       </c>
       <c r="C18" t="n">
-        <v>1112</v>
+        <v>1205</v>
       </c>
       <c r="D18" t="n">
-        <v>968</v>
+        <v>1153</v>
       </c>
       <c r="E18" t="n">
-        <v>1233</v>
+        <v>1032</v>
       </c>
       <c r="F18" t="n">
-        <v>1040</v>
+        <v>1163</v>
       </c>
       <c r="G18" t="n">
-        <v>1069</v>
+        <v>1019</v>
       </c>
       <c r="H18" t="n">
-        <v>1025</v>
+        <v>1048</v>
       </c>
       <c r="I18" t="n">
-        <v>992</v>
+        <v>1142</v>
       </c>
       <c r="J18" t="n">
-        <v>1083</v>
+        <v>865</v>
       </c>
       <c r="K18" t="n">
-        <v>1135</v>
+        <v>1174</v>
       </c>
       <c r="L18" t="n">
-        <v>1063.3</v>
+        <v>1090.8</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1304</v>
+        <v>1140</v>
       </c>
       <c r="C19" t="n">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D19" t="n">
-        <v>1089</v>
+        <v>1351</v>
       </c>
       <c r="E19" t="n">
-        <v>1133</v>
+        <v>1300</v>
       </c>
       <c r="F19" t="n">
-        <v>1254</v>
+        <v>1190</v>
       </c>
       <c r="G19" t="n">
-        <v>1173</v>
+        <v>1111</v>
       </c>
       <c r="H19" t="n">
-        <v>1215</v>
+        <v>1164</v>
       </c>
       <c r="I19" t="n">
-        <v>1252</v>
+        <v>1237</v>
       </c>
       <c r="J19" t="n">
-        <v>1209</v>
+        <v>1174</v>
       </c>
       <c r="K19" t="n">
-        <v>1244</v>
+        <v>1202</v>
       </c>
       <c r="L19" t="n">
-        <v>1206.8</v>
+        <v>1206.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1073</v>
+        <v>1097</v>
       </c>
       <c r="C20" t="n">
-        <v>1091</v>
+        <v>984</v>
       </c>
       <c r="D20" t="n">
-        <v>1102</v>
+        <v>1127</v>
       </c>
       <c r="E20" t="n">
-        <v>1230</v>
+        <v>1067</v>
       </c>
       <c r="F20" t="n">
-        <v>1084</v>
+        <v>1051</v>
       </c>
       <c r="G20" t="n">
-        <v>1081</v>
+        <v>973</v>
       </c>
       <c r="H20" t="n">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="I20" t="n">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="J20" t="n">
-        <v>1064</v>
+        <v>1279</v>
       </c>
       <c r="K20" t="n">
-        <v>1090</v>
+        <v>1061</v>
       </c>
       <c r="L20" t="n">
-        <v>1117.3</v>
+        <v>1099.7</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="C21" t="n">
-        <v>1096</v>
+        <v>1288</v>
       </c>
       <c r="D21" t="n">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="E21" t="n">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="F21" t="n">
-        <v>1088</v>
+        <v>1027</v>
       </c>
       <c r="G21" t="n">
-        <v>1242</v>
+        <v>1107</v>
       </c>
       <c r="H21" t="n">
-        <v>1105</v>
+        <v>1128</v>
       </c>
       <c r="I21" t="n">
-        <v>1256</v>
+        <v>1011</v>
       </c>
       <c r="J21" t="n">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="K21" t="n">
-        <v>1002</v>
+        <v>1148</v>
       </c>
       <c r="L21" t="n">
-        <v>1124.2</v>
+        <v>1122.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1063</v>
+        <v>1237</v>
       </c>
       <c r="C22" t="n">
-        <v>1193</v>
+        <v>1274</v>
       </c>
       <c r="D22" t="n">
-        <v>1034</v>
+        <v>1144</v>
       </c>
       <c r="E22" t="n">
-        <v>1247</v>
+        <v>1052</v>
       </c>
       <c r="F22" t="n">
-        <v>1412</v>
+        <v>1148</v>
       </c>
       <c r="G22" t="n">
-        <v>1132</v>
+        <v>1175</v>
       </c>
       <c r="H22" t="n">
-        <v>1229</v>
+        <v>1253</v>
       </c>
       <c r="I22" t="n">
-        <v>1113</v>
+        <v>1215</v>
       </c>
       <c r="J22" t="n">
-        <v>1305</v>
+        <v>1169</v>
       </c>
       <c r="K22" t="n">
-        <v>1186</v>
+        <v>1216</v>
       </c>
       <c r="L22" t="n">
-        <v>1191.4</v>
+        <v>1188.3</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1156</v>
+        <v>1016</v>
       </c>
       <c r="C23" t="n">
-        <v>1053</v>
+        <v>1215</v>
       </c>
       <c r="D23" t="n">
-        <v>1016</v>
+        <v>1066</v>
       </c>
       <c r="E23" t="n">
-        <v>1052</v>
+        <v>978</v>
       </c>
       <c r="F23" t="n">
+        <v>993</v>
+      </c>
+      <c r="G23" t="n">
         <v>987</v>
       </c>
-      <c r="G23" t="n">
-        <v>944</v>
-      </c>
       <c r="H23" t="n">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="I23" t="n">
-        <v>1101</v>
+        <v>952</v>
       </c>
       <c r="J23" t="n">
-        <v>927</v>
+        <v>1045</v>
       </c>
       <c r="K23" t="n">
-        <v>1203</v>
+        <v>997</v>
       </c>
       <c r="L23" t="n">
-        <v>1051.9</v>
+        <v>1029.9</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1040</v>
+        <v>1459</v>
       </c>
       <c r="C24" t="n">
-        <v>1265</v>
+        <v>984</v>
       </c>
       <c r="D24" t="n">
+        <v>998</v>
+      </c>
+      <c r="E24" t="n">
         <v>1111</v>
       </c>
-      <c r="E24" t="n">
-        <v>1259</v>
-      </c>
       <c r="F24" t="n">
-        <v>1144</v>
+        <v>1102</v>
       </c>
       <c r="G24" t="n">
-        <v>1239</v>
+        <v>1155</v>
       </c>
       <c r="H24" t="n">
-        <v>1312</v>
+        <v>1043</v>
       </c>
       <c r="I24" t="n">
-        <v>1355</v>
+        <v>1171</v>
       </c>
       <c r="J24" t="n">
-        <v>1351</v>
+        <v>1132</v>
       </c>
       <c r="K24" t="n">
-        <v>1202</v>
+        <v>1037</v>
       </c>
       <c r="L24" t="n">
-        <v>1227.8</v>
+        <v>1119.2</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1131</v>
+        <v>1239</v>
       </c>
       <c r="C25" t="n">
-        <v>1336</v>
+        <v>1176</v>
       </c>
       <c r="D25" t="n">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="E25" t="n">
-        <v>1119</v>
+        <v>1176</v>
       </c>
       <c r="F25" t="n">
-        <v>1063</v>
+        <v>1234</v>
       </c>
       <c r="G25" t="n">
-        <v>1093</v>
+        <v>1052</v>
       </c>
       <c r="H25" t="n">
-        <v>1314</v>
+        <v>1236</v>
       </c>
       <c r="I25" t="n">
-        <v>1283</v>
+        <v>1050</v>
       </c>
       <c r="J25" t="n">
-        <v>1299</v>
+        <v>1373</v>
       </c>
       <c r="K25" t="n">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="L25" t="n">
-        <v>1228.6</v>
+        <v>1218.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1018</v>
+        <v>1073</v>
       </c>
       <c r="C26" t="n">
-        <v>981</v>
+        <v>929</v>
       </c>
       <c r="D26" t="n">
-        <v>973</v>
+        <v>1137</v>
       </c>
       <c r="E26" t="n">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="F26" t="n">
-        <v>984</v>
+        <v>1001</v>
       </c>
       <c r="G26" t="n">
-        <v>1139</v>
+        <v>1109</v>
       </c>
       <c r="H26" t="n">
-        <v>952</v>
+        <v>1067</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="J26" t="n">
-        <v>986</v>
+        <v>1106</v>
       </c>
       <c r="K26" t="n">
-        <v>1115</v>
+        <v>1010</v>
       </c>
       <c r="L26" t="n">
-        <v>1011.7</v>
+        <v>1048.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1231</v>
+        <v>1289</v>
       </c>
       <c r="C27" t="n">
+        <v>1293</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1107</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1068</v>
+      </c>
+      <c r="G27" t="n">
         <v>1159</v>
       </c>
-      <c r="D27" t="n">
-        <v>1184</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1139</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1187</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1202</v>
-      </c>
       <c r="H27" t="n">
-        <v>1214</v>
+        <v>1081</v>
       </c>
       <c r="I27" t="n">
-        <v>1280</v>
+        <v>1351</v>
       </c>
       <c r="J27" t="n">
-        <v>1131</v>
+        <v>1194</v>
       </c>
       <c r="K27" t="n">
-        <v>1100</v>
+        <v>1208</v>
       </c>
       <c r="L27" t="n">
-        <v>1182.7</v>
+        <v>1190.4</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1105</v>
+        <v>1049</v>
       </c>
       <c r="C28" t="n">
-        <v>959</v>
+        <v>1049</v>
       </c>
       <c r="D28" t="n">
-        <v>998</v>
+        <v>1058</v>
       </c>
       <c r="E28" t="n">
-        <v>1088</v>
+        <v>1138</v>
       </c>
       <c r="F28" t="n">
-        <v>922</v>
+        <v>1147</v>
       </c>
       <c r="G28" t="n">
-        <v>1155</v>
+        <v>1060</v>
       </c>
       <c r="H28" t="n">
-        <v>1014</v>
+        <v>1192</v>
       </c>
       <c r="I28" t="n">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="J28" t="n">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="K28" t="n">
-        <v>1060</v>
+        <v>937</v>
       </c>
       <c r="L28" t="n">
-        <v>1059.7</v>
+        <v>1093.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1131</v>
+        <v>1019</v>
       </c>
       <c r="C29" t="n">
-        <v>997</v>
+        <v>1055</v>
       </c>
       <c r="D29" t="n">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="E29" t="n">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="F29" t="n">
-        <v>1068</v>
+        <v>979</v>
       </c>
       <c r="G29" t="n">
-        <v>1038</v>
+        <v>1072</v>
       </c>
       <c r="H29" t="n">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="I29" t="n">
-        <v>1131</v>
+        <v>1186</v>
       </c>
       <c r="J29" t="n">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="K29" t="n">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="L29" t="n">
-        <v>1055.4</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>995</v>
+        <v>916</v>
       </c>
       <c r="C30" t="n">
-        <v>1052</v>
+        <v>899</v>
       </c>
       <c r="D30" t="n">
-        <v>972</v>
+        <v>940</v>
       </c>
       <c r="E30" t="n">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="F30" t="n">
-        <v>1203</v>
+        <v>1001</v>
       </c>
       <c r="G30" t="n">
-        <v>1218</v>
+        <v>904</v>
       </c>
       <c r="H30" t="n">
-        <v>1115</v>
+        <v>1062</v>
       </c>
       <c r="I30" t="n">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="J30" t="n">
-        <v>1010</v>
+        <v>1073</v>
       </c>
       <c r="K30" t="n">
-        <v>1152</v>
+        <v>1064</v>
       </c>
       <c r="L30" t="n">
-        <v>1077.5</v>
+        <v>995.5</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1116</v>
+        <v>1156</v>
       </c>
       <c r="C31" t="n">
-        <v>1225</v>
+        <v>1378</v>
       </c>
       <c r="D31" t="n">
-        <v>1150</v>
+        <v>1052</v>
       </c>
       <c r="E31" t="n">
-        <v>1240</v>
+        <v>1184</v>
       </c>
       <c r="F31" t="n">
-        <v>1188</v>
+        <v>1224</v>
       </c>
       <c r="G31" t="n">
-        <v>1149</v>
+        <v>1223</v>
       </c>
       <c r="H31" t="n">
-        <v>1308</v>
+        <v>1002</v>
       </c>
       <c r="I31" t="n">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="J31" t="n">
-        <v>1178</v>
+        <v>1019</v>
       </c>
       <c r="K31" t="n">
-        <v>1304</v>
+        <v>1449</v>
       </c>
       <c r="L31" t="n">
-        <v>1197.7</v>
+        <v>1181.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1032</v>
+        <v>986</v>
       </c>
       <c r="C32" t="n">
-        <v>1017</v>
+        <v>859</v>
       </c>
       <c r="D32" t="n">
-        <v>1175</v>
+        <v>1283</v>
       </c>
       <c r="E32" t="n">
-        <v>938</v>
+        <v>994</v>
       </c>
       <c r="F32" t="n">
-        <v>1041</v>
+        <v>920</v>
       </c>
       <c r="G32" t="n">
-        <v>1154</v>
+        <v>991</v>
       </c>
       <c r="H32" t="n">
-        <v>1297</v>
+        <v>977</v>
       </c>
       <c r="I32" t="n">
         <v>1056</v>
       </c>
       <c r="J32" t="n">
-        <v>1009</v>
+        <v>973</v>
       </c>
       <c r="K32" t="n">
-        <v>977</v>
+        <v>1038</v>
       </c>
       <c r="L32" t="n">
-        <v>1069.6</v>
+        <v>1007.7</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>992</v>
+        <v>1019</v>
       </c>
       <c r="C33" t="n">
-        <v>1068</v>
+        <v>1320</v>
       </c>
       <c r="D33" t="n">
-        <v>1183</v>
+        <v>1002</v>
       </c>
       <c r="E33" t="n">
-        <v>1079</v>
+        <v>962</v>
       </c>
       <c r="F33" t="n">
-        <v>1101</v>
+        <v>1074</v>
       </c>
       <c r="G33" t="n">
-        <v>1054</v>
+        <v>1136</v>
       </c>
       <c r="H33" t="n">
-        <v>1081</v>
+        <v>1100</v>
       </c>
       <c r="I33" t="n">
-        <v>1124</v>
+        <v>1243</v>
       </c>
       <c r="J33" t="n">
-        <v>1153</v>
+        <v>1222</v>
       </c>
       <c r="K33" t="n">
-        <v>1038</v>
+        <v>1016</v>
       </c>
       <c r="L33" t="n">
-        <v>1087.3</v>
+        <v>1109.4</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1111</v>
+        <v>1024</v>
       </c>
       <c r="C34" t="n">
-        <v>1130</v>
+        <v>1017</v>
       </c>
       <c r="D34" t="n">
-        <v>1060</v>
+        <v>1038</v>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>1084</v>
       </c>
       <c r="F34" t="n">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="G34" t="n">
-        <v>1139</v>
+        <v>1177</v>
       </c>
       <c r="H34" t="n">
-        <v>1087</v>
+        <v>1169</v>
       </c>
       <c r="I34" t="n">
-        <v>1302</v>
+        <v>1134</v>
       </c>
       <c r="J34" t="n">
-        <v>1261</v>
+        <v>1007</v>
       </c>
       <c r="K34" t="n">
-        <v>1321</v>
+        <v>1023</v>
       </c>
       <c r="L34" t="n">
-        <v>1162.9</v>
+        <v>1079.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
+        <v>1136</v>
+      </c>
+      <c r="C35" t="n">
         <v>1064</v>
       </c>
-      <c r="C35" t="n">
-        <v>994</v>
-      </c>
       <c r="D35" t="n">
-        <v>1077</v>
+        <v>987</v>
       </c>
       <c r="E35" t="n">
-        <v>1082</v>
+        <v>1061</v>
       </c>
       <c r="F35" t="n">
-        <v>1018</v>
+        <v>1234</v>
       </c>
       <c r="G35" t="n">
-        <v>1166</v>
+        <v>1183</v>
       </c>
       <c r="H35" t="n">
-        <v>1090</v>
+        <v>1202</v>
       </c>
       <c r="I35" t="n">
-        <v>1141</v>
+        <v>1033</v>
       </c>
       <c r="J35" t="n">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="K35" t="n">
-        <v>1005</v>
+        <v>1104</v>
       </c>
       <c r="L35" t="n">
-        <v>1075.1</v>
+        <v>1112.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1270</v>
+        <v>1178</v>
       </c>
       <c r="C36" t="n">
-        <v>1170</v>
+        <v>1010</v>
       </c>
       <c r="D36" t="n">
-        <v>1058</v>
+        <v>1150</v>
       </c>
       <c r="E36" t="n">
-        <v>1178</v>
+        <v>1116</v>
       </c>
       <c r="F36" t="n">
-        <v>979</v>
+        <v>1189</v>
       </c>
       <c r="G36" t="n">
-        <v>1035</v>
+        <v>980</v>
       </c>
       <c r="H36" t="n">
-        <v>1119</v>
+        <v>1075</v>
       </c>
       <c r="I36" t="n">
-        <v>1078</v>
+        <v>1018</v>
       </c>
       <c r="J36" t="n">
-        <v>1186</v>
+        <v>1049</v>
       </c>
       <c r="K36" t="n">
-        <v>1164</v>
+        <v>1323</v>
       </c>
       <c r="L36" t="n">
-        <v>1123.7</v>
+        <v>1108.8</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1056</v>
+        <v>1066</v>
       </c>
       <c r="C37" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1047</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1117</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1162</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1108</v>
+      </c>
+      <c r="I37" t="n">
+        <v>975</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1033</v>
+      </c>
+      <c r="K37" t="n">
         <v>997</v>
       </c>
-      <c r="D37" t="n">
-        <v>1105</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1025</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1088</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1056</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1180</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1073</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1172</v>
-      </c>
-      <c r="K37" t="n">
-        <v>990</v>
-      </c>
       <c r="L37" t="n">
-        <v>1074.2</v>
+        <v>1075.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1095</v>
+        <v>1139</v>
       </c>
       <c r="C38" t="n">
-        <v>1064</v>
+        <v>1039</v>
       </c>
       <c r="D38" t="n">
-        <v>1120</v>
+        <v>1104</v>
       </c>
       <c r="E38" t="n">
-        <v>906</v>
+        <v>1229</v>
       </c>
       <c r="F38" t="n">
-        <v>1107</v>
+        <v>929</v>
       </c>
       <c r="G38" t="n">
-        <v>974</v>
+        <v>1076</v>
       </c>
       <c r="H38" t="n">
-        <v>1022</v>
+        <v>1262</v>
       </c>
       <c r="I38" t="n">
-        <v>1007</v>
+        <v>968</v>
       </c>
       <c r="J38" t="n">
-        <v>916</v>
+        <v>993</v>
       </c>
       <c r="K38" t="n">
-        <v>956</v>
+        <v>1083</v>
       </c>
       <c r="L38" t="n">
-        <v>1016.7</v>
+        <v>1082.2</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1036</v>
+        <v>1075</v>
       </c>
       <c r="C39" t="n">
-        <v>1017</v>
+        <v>1180</v>
       </c>
       <c r="D39" t="n">
-        <v>963</v>
+        <v>1077</v>
       </c>
       <c r="E39" t="n">
-        <v>1126</v>
+        <v>954</v>
       </c>
       <c r="F39" t="n">
-        <v>1226</v>
+        <v>1045</v>
       </c>
       <c r="G39" t="n">
-        <v>1041</v>
+        <v>975</v>
       </c>
       <c r="H39" t="n">
-        <v>1017</v>
+        <v>1153</v>
       </c>
       <c r="I39" t="n">
-        <v>1151</v>
+        <v>1074</v>
       </c>
       <c r="J39" t="n">
-        <v>998</v>
+        <v>1178</v>
       </c>
       <c r="K39" t="n">
-        <v>924</v>
+        <v>1147</v>
       </c>
       <c r="L39" t="n">
-        <v>1049.9</v>
+        <v>1085.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1072</v>
+        <v>1189</v>
       </c>
       <c r="C40" t="n">
-        <v>1085</v>
+        <v>1120</v>
       </c>
       <c r="D40" t="n">
-        <v>1058</v>
+        <v>1220</v>
       </c>
       <c r="E40" t="n">
-        <v>1066</v>
+        <v>1161</v>
       </c>
       <c r="F40" t="n">
-        <v>1056</v>
+        <v>1200</v>
       </c>
       <c r="G40" t="n">
-        <v>1252</v>
+        <v>1213</v>
       </c>
       <c r="H40" t="n">
-        <v>1110</v>
+        <v>1009</v>
       </c>
       <c r="I40" t="n">
-        <v>1207</v>
+        <v>1184</v>
       </c>
       <c r="J40" t="n">
-        <v>1095</v>
+        <v>1138</v>
       </c>
       <c r="K40" t="n">
-        <v>1069</v>
+        <v>1132</v>
       </c>
       <c r="L40" t="n">
-        <v>1107</v>
+        <v>1156.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1136</v>
+        <v>1026</v>
       </c>
       <c r="C41" t="n">
-        <v>1204</v>
+        <v>1251</v>
       </c>
       <c r="D41" t="n">
-        <v>990</v>
+        <v>1063</v>
       </c>
       <c r="E41" t="n">
-        <v>1079</v>
+        <v>1040</v>
       </c>
       <c r="F41" t="n">
-        <v>874</v>
+        <v>1083</v>
       </c>
       <c r="G41" t="n">
-        <v>1015</v>
+        <v>1129</v>
       </c>
       <c r="H41" t="n">
-        <v>1234</v>
+        <v>1011</v>
       </c>
       <c r="I41" t="n">
-        <v>978</v>
+        <v>895</v>
       </c>
       <c r="J41" t="n">
-        <v>1093</v>
+        <v>1179</v>
       </c>
       <c r="K41" t="n">
-        <v>965</v>
+        <v>1023</v>
       </c>
       <c r="L41" t="n">
-        <v>1056.8</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="C42" t="n">
-        <v>987</v>
+        <v>1175</v>
       </c>
       <c r="D42" t="n">
-        <v>1168</v>
+        <v>1212</v>
       </c>
       <c r="E42" t="n">
+        <v>1185</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G42" t="n">
         <v>1015</v>
       </c>
-      <c r="F42" t="n">
-        <v>1111</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1110</v>
-      </c>
       <c r="H42" t="n">
+        <v>1038</v>
+      </c>
+      <c r="I42" t="n">
         <v>1010</v>
       </c>
-      <c r="I42" t="n">
-        <v>1104</v>
-      </c>
       <c r="J42" t="n">
-        <v>1073</v>
+        <v>999</v>
       </c>
       <c r="K42" t="n">
-        <v>1051</v>
+        <v>1175</v>
       </c>
       <c r="L42" t="n">
-        <v>1072.2</v>
+        <v>1110.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1196</v>
+        <v>1014</v>
       </c>
       <c r="C43" t="n">
-        <v>1131</v>
+        <v>1005</v>
       </c>
       <c r="D43" t="n">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="E43" t="n">
-        <v>1195</v>
+        <v>1172</v>
       </c>
       <c r="F43" t="n">
-        <v>1171</v>
+        <v>1192</v>
       </c>
       <c r="G43" t="n">
-        <v>1082</v>
+        <v>1262</v>
       </c>
       <c r="H43" t="n">
-        <v>1086</v>
+        <v>1188</v>
       </c>
       <c r="I43" t="n">
-        <v>1007</v>
+        <v>1242</v>
       </c>
       <c r="J43" t="n">
-        <v>1171</v>
+        <v>1065</v>
       </c>
       <c r="K43" t="n">
-        <v>981</v>
+        <v>1211</v>
       </c>
       <c r="L43" t="n">
-        <v>1110.8</v>
+        <v>1144.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1180</v>
+        <v>956</v>
       </c>
       <c r="C44" t="n">
-        <v>1088</v>
+        <v>1215</v>
       </c>
       <c r="D44" t="n">
-        <v>1044</v>
+        <v>1133</v>
       </c>
       <c r="E44" t="n">
-        <v>1238</v>
+        <v>1183</v>
       </c>
       <c r="F44" t="n">
-        <v>1024</v>
+        <v>1114</v>
       </c>
       <c r="G44" t="n">
-        <v>1001</v>
+        <v>983</v>
       </c>
       <c r="H44" t="n">
-        <v>1081</v>
+        <v>1305</v>
       </c>
       <c r="I44" t="n">
-        <v>994</v>
+        <v>1032</v>
       </c>
       <c r="J44" t="n">
-        <v>1110</v>
+        <v>924</v>
       </c>
       <c r="K44" t="n">
-        <v>1291</v>
+        <v>1037</v>
       </c>
       <c r="L44" t="n">
-        <v>1105.1</v>
+        <v>1088.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1130</v>
+        <v>1053</v>
       </c>
       <c r="C45" t="n">
-        <v>996</v>
+        <v>1109</v>
       </c>
       <c r="D45" t="n">
-        <v>1092</v>
+        <v>1063</v>
       </c>
       <c r="E45" t="n">
-        <v>1244</v>
+        <v>1107</v>
       </c>
       <c r="F45" t="n">
-        <v>1220</v>
+        <v>1150</v>
       </c>
       <c r="G45" t="n">
-        <v>1107</v>
+        <v>1298</v>
       </c>
       <c r="H45" t="n">
-        <v>1215</v>
+        <v>1155</v>
       </c>
       <c r="I45" t="n">
-        <v>1195</v>
+        <v>1266</v>
       </c>
       <c r="J45" t="n">
-        <v>1147</v>
+        <v>1228</v>
       </c>
       <c r="K45" t="n">
-        <v>1118</v>
+        <v>1277</v>
       </c>
       <c r="L45" t="n">
-        <v>1146.4</v>
+        <v>1170.6</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1278</v>
+        <v>1068</v>
       </c>
       <c r="C46" t="n">
-        <v>1270</v>
+        <v>1202</v>
       </c>
       <c r="D46" t="n">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E46" t="n">
-        <v>1113</v>
+        <v>1214</v>
       </c>
       <c r="F46" t="n">
-        <v>1060</v>
+        <v>1193</v>
       </c>
       <c r="G46" t="n">
-        <v>1012</v>
+        <v>1104</v>
       </c>
       <c r="H46" t="n">
-        <v>1058</v>
+        <v>1130</v>
       </c>
       <c r="I46" t="n">
-        <v>1227</v>
+        <v>1182</v>
       </c>
       <c r="J46" t="n">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="K46" t="n">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="L46" t="n">
-        <v>1149.3</v>
+        <v>1155.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1189</v>
+        <v>1078</v>
       </c>
       <c r="C47" t="n">
-        <v>1259</v>
+        <v>1185</v>
       </c>
       <c r="D47" t="n">
-        <v>1144</v>
+        <v>1099</v>
       </c>
       <c r="E47" t="n">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="F47" t="n">
-        <v>1298</v>
+        <v>1326</v>
       </c>
       <c r="G47" t="n">
-        <v>1159</v>
+        <v>1034</v>
       </c>
       <c r="H47" t="n">
-        <v>1243</v>
+        <v>1202</v>
       </c>
       <c r="I47" t="n">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="J47" t="n">
-        <v>1134</v>
+        <v>1125</v>
       </c>
       <c r="K47" t="n">
-        <v>1108</v>
+        <v>1057</v>
       </c>
       <c r="L47" t="n">
-        <v>1207.4</v>
+        <v>1165.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1172</v>
+        <v>1248</v>
       </c>
       <c r="C48" t="n">
-        <v>1142</v>
+        <v>1112</v>
       </c>
       <c r="D48" t="n">
-        <v>1165</v>
+        <v>1103</v>
       </c>
       <c r="E48" t="n">
+        <v>1113</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1163</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1222</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1099</v>
+      </c>
+      <c r="I48" t="n">
         <v>1108</v>
       </c>
-      <c r="F48" t="n">
-        <v>1107</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1123</v>
-      </c>
-      <c r="H48" t="n">
-        <v>1052</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1085</v>
-      </c>
       <c r="J48" t="n">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="K48" t="n">
-        <v>1119</v>
+        <v>1252</v>
       </c>
       <c r="L48" t="n">
-        <v>1119.8</v>
+        <v>1155.2</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>973</v>
+        <v>1135</v>
       </c>
       <c r="C49" t="n">
-        <v>1202</v>
+        <v>1061</v>
       </c>
       <c r="D49" t="n">
-        <v>1209</v>
+        <v>1045</v>
       </c>
       <c r="E49" t="n">
-        <v>1065</v>
+        <v>1041</v>
       </c>
       <c r="F49" t="n">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="G49" t="n">
-        <v>1175</v>
+        <v>1022</v>
       </c>
       <c r="H49" t="n">
-        <v>1145</v>
+        <v>1189</v>
       </c>
       <c r="I49" t="n">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="J49" t="n">
-        <v>1029</v>
+        <v>1156</v>
       </c>
       <c r="K49" t="n">
-        <v>1116</v>
+        <v>1238</v>
       </c>
       <c r="L49" t="n">
-        <v>1097.6</v>
+        <v>1099.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1002</v>
+        <v>1077</v>
       </c>
       <c r="C50" t="n">
-        <v>1086</v>
+        <v>1050</v>
       </c>
       <c r="D50" t="n">
-        <v>986</v>
+        <v>1168</v>
       </c>
       <c r="E50" t="n">
-        <v>1012</v>
+        <v>925</v>
       </c>
       <c r="F50" t="n">
-        <v>1012</v>
+        <v>1112</v>
       </c>
       <c r="G50" t="n">
-        <v>989</v>
+        <v>1077</v>
       </c>
       <c r="H50" t="n">
-        <v>1113</v>
+        <v>1320</v>
       </c>
       <c r="I50" t="n">
-        <v>916</v>
+        <v>959</v>
       </c>
       <c r="J50" t="n">
-        <v>1160</v>
+        <v>1008</v>
       </c>
       <c r="K50" t="n">
-        <v>1075</v>
+        <v>937</v>
       </c>
       <c r="L50" t="n">
-        <v>1035.1</v>
+        <v>1063.3</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1065</v>
+        <v>1098</v>
       </c>
       <c r="C51" t="n">
-        <v>1176</v>
+        <v>956</v>
       </c>
       <c r="D51" t="n">
-        <v>996</v>
+        <v>1049</v>
       </c>
       <c r="E51" t="n">
-        <v>1053</v>
+        <v>1082</v>
       </c>
       <c r="F51" t="n">
-        <v>1099</v>
+        <v>1048</v>
       </c>
       <c r="G51" t="n">
-        <v>1057</v>
+        <v>989</v>
       </c>
       <c r="H51" t="n">
-        <v>965</v>
+        <v>1108</v>
       </c>
       <c r="I51" t="n">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="J51" t="n">
-        <v>993</v>
+        <v>1265</v>
       </c>
       <c r="K51" t="n">
-        <v>998</v>
+        <v>1151</v>
       </c>
       <c r="L51" t="n">
-        <v>1043.8</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1107.48</v>
+        <v>1110.18</v>
       </c>
       <c r="C52" t="n">
-        <v>1105.88</v>
+        <v>1098.46</v>
       </c>
       <c r="D52" t="n">
-        <v>1087.4</v>
+        <v>1101.64</v>
       </c>
       <c r="E52" t="n">
-        <v>1104.3</v>
+        <v>1093.18</v>
       </c>
       <c r="F52" t="n">
-        <v>1100.36</v>
+        <v>1108.38</v>
       </c>
       <c r="G52" t="n">
-        <v>1095.4</v>
+        <v>1089.24</v>
       </c>
       <c r="H52" t="n">
-        <v>1116.52</v>
+        <v>1117.02</v>
       </c>
       <c r="I52" t="n">
-        <v>1126.88</v>
+        <v>1109.68</v>
       </c>
       <c r="J52" t="n">
-        <v>1111.76</v>
+        <v>1105.72</v>
       </c>
       <c r="K52" t="n">
-        <v>1109.6</v>
+        <v>1111.56</v>
       </c>
       <c r="L52" t="n">
-        <v>1106.558</v>
+        <v>1104.506</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>13.27621293067932</v>
+        <v>15.91698241233826</v>
       </c>
       <c r="C2" t="n">
-        <v>13.12205576896667</v>
+        <v>12.46623682975769</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8408682346344</v>
+        <v>15.69253611564636</v>
       </c>
       <c r="E2" t="n">
-        <v>11.47028470039368</v>
+        <v>13.30908608436584</v>
       </c>
       <c r="F2" t="n">
-        <v>12.24086904525757</v>
+        <v>15.93290328979492</v>
       </c>
       <c r="G2" t="n">
-        <v>14.60380673408508</v>
+        <v>13.17842721939087</v>
       </c>
       <c r="H2" t="n">
-        <v>13.62478446960449</v>
+        <v>14.6147575378418</v>
       </c>
       <c r="I2" t="n">
-        <v>13.54051423072815</v>
+        <v>12.7036349773407</v>
       </c>
       <c r="J2" t="n">
-        <v>11.81440544128418</v>
+        <v>13.09112453460693</v>
       </c>
       <c r="K2" t="n">
-        <v>11.28777050971985</v>
+        <v>13.55096745491028</v>
       </c>
       <c r="L2" t="n">
-        <v>12.68215720653534</v>
+        <v>14.04566564559937</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>10.17609024047852</v>
+        <v>13.71254801750183</v>
       </c>
       <c r="C3" t="n">
-        <v>9.994046211242676</v>
+        <v>11.89814639091492</v>
       </c>
       <c r="D3" t="n">
-        <v>10.23694539070129</v>
+        <v>14.20978689193726</v>
       </c>
       <c r="E3" t="n">
-        <v>9.809053659439087</v>
+        <v>11.69320344924927</v>
       </c>
       <c r="F3" t="n">
-        <v>11.36105680465698</v>
+        <v>12.19196605682373</v>
       </c>
       <c r="G3" t="n">
-        <v>10.2044882774353</v>
+        <v>11.07776641845703</v>
       </c>
       <c r="H3" t="n">
-        <v>10.22595047950745</v>
+        <v>11.4832501411438</v>
       </c>
       <c r="I3" t="n">
-        <v>11.01095199584961</v>
+        <v>14.73834848403931</v>
       </c>
       <c r="J3" t="n">
-        <v>14.1105432510376</v>
+        <v>13.44474840164185</v>
       </c>
       <c r="K3" t="n">
-        <v>13.66118478775024</v>
+        <v>12.23778057098389</v>
       </c>
       <c r="L3" t="n">
-        <v>11.07903110980988</v>
+        <v>12.66875448226929</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>11.93709444999695</v>
+        <v>18.12243247032166</v>
       </c>
       <c r="C4" t="n">
-        <v>15.27571129798889</v>
+        <v>14.60190486907959</v>
       </c>
       <c r="D4" t="n">
-        <v>15.97495079040527</v>
+        <v>14.13155150413513</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91064262390137</v>
+        <v>15.47757649421692</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7729229927063</v>
+        <v>11.91317343711853</v>
       </c>
       <c r="G4" t="n">
-        <v>13.92451047897339</v>
+        <v>13.44769406318665</v>
       </c>
       <c r="H4" t="n">
-        <v>12.82191157341003</v>
+        <v>15.38854813575745</v>
       </c>
       <c r="I4" t="n">
-        <v>15.5873327255249</v>
+        <v>16.05629253387451</v>
       </c>
       <c r="J4" t="n">
-        <v>11.62141418457031</v>
+        <v>17.86849808692932</v>
       </c>
       <c r="K4" t="n">
-        <v>17.71452403068542</v>
+        <v>14.03663873672485</v>
       </c>
       <c r="L4" t="n">
-        <v>14.15410151481628</v>
+        <v>15.10443103313446</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>10.22643208503723</v>
+        <v>12.11569881439209</v>
       </c>
       <c r="C5" t="n">
-        <v>10.37752556800842</v>
+        <v>15.7816903591156</v>
       </c>
       <c r="D5" t="n">
-        <v>10.66310739517212</v>
+        <v>12.31135249137878</v>
       </c>
       <c r="E5" t="n">
-        <v>10.73127102851868</v>
+        <v>18.13977432250977</v>
       </c>
       <c r="F5" t="n">
-        <v>11.09972262382507</v>
+        <v>12.6040096282959</v>
       </c>
       <c r="G5" t="n">
-        <v>10.03147268295288</v>
+        <v>12.06512665748596</v>
       </c>
       <c r="H5" t="n">
-        <v>10.73568820953369</v>
+        <v>12.32596778869629</v>
       </c>
       <c r="I5" t="n">
-        <v>11.60594916343689</v>
+        <v>12.51268315315247</v>
       </c>
       <c r="J5" t="n">
-        <v>11.3957188129425</v>
+        <v>13.75444841384888</v>
       </c>
       <c r="K5" t="n">
-        <v>10.61313199996948</v>
+        <v>10.31819844245911</v>
       </c>
       <c r="L5" t="n">
-        <v>10.7480019569397</v>
+        <v>13.19289500713348</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>13.87987232208252</v>
+        <v>15.02074551582336</v>
       </c>
       <c r="C6" t="n">
-        <v>11.80837059020996</v>
+        <v>15.17385745048523</v>
       </c>
       <c r="D6" t="n">
-        <v>11.22283530235291</v>
+        <v>14.37444043159485</v>
       </c>
       <c r="E6" t="n">
-        <v>12.17731785774231</v>
+        <v>12.47719955444336</v>
       </c>
       <c r="F6" t="n">
-        <v>10.93503093719482</v>
+        <v>11.49424529075623</v>
       </c>
       <c r="G6" t="n">
-        <v>13.84494233131409</v>
+        <v>12.37400841712952</v>
       </c>
       <c r="H6" t="n">
-        <v>11.70109176635742</v>
+        <v>17.07648348808289</v>
       </c>
       <c r="I6" t="n">
-        <v>17.17115354537964</v>
+        <v>11.8010265827179</v>
       </c>
       <c r="J6" t="n">
-        <v>11.84387302398682</v>
+        <v>11.91666626930237</v>
       </c>
       <c r="K6" t="n">
-        <v>11.70031142234802</v>
+        <v>13.04728722572327</v>
       </c>
       <c r="L6" t="n">
-        <v>12.62847990989685</v>
+        <v>13.4755960226059</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>12.9328281879425</v>
+        <v>11.91413760185242</v>
       </c>
       <c r="C7" t="n">
-        <v>11.91748070716858</v>
+        <v>13.71556806564331</v>
       </c>
       <c r="D7" t="n">
-        <v>11.67912268638611</v>
+        <v>12.91442942619324</v>
       </c>
       <c r="E7" t="n">
-        <v>13.15625333786011</v>
+        <v>15.63330793380737</v>
       </c>
       <c r="F7" t="n">
-        <v>14.17860150337219</v>
+        <v>11.78984570503235</v>
       </c>
       <c r="G7" t="n">
-        <v>10.60421848297119</v>
+        <v>11.24375486373901</v>
       </c>
       <c r="H7" t="n">
-        <v>13.93497824668884</v>
+        <v>11.52453589439392</v>
       </c>
       <c r="I7" t="n">
-        <v>11.36455130577087</v>
+        <v>11.37041616439819</v>
       </c>
       <c r="J7" t="n">
-        <v>10.41847920417786</v>
+        <v>12.88826966285706</v>
       </c>
       <c r="K7" t="n">
-        <v>13.83872437477112</v>
+        <v>11.8164496421814</v>
       </c>
       <c r="L7" t="n">
-        <v>12.40252380371094</v>
+        <v>12.48107149600983</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2348461151123</v>
+        <v>11.6627893447876</v>
       </c>
       <c r="C8" t="n">
-        <v>11.60492610931396</v>
+        <v>12.00645732879639</v>
       </c>
       <c r="D8" t="n">
-        <v>15.03267669677734</v>
+        <v>11.87924599647522</v>
       </c>
       <c r="E8" t="n">
-        <v>14.69310522079468</v>
+        <v>12.36442923545837</v>
       </c>
       <c r="F8" t="n">
-        <v>13.62524628639221</v>
+        <v>12.05821585655212</v>
       </c>
       <c r="G8" t="n">
-        <v>13.01792001724243</v>
+        <v>11.91450381278992</v>
       </c>
       <c r="H8" t="n">
-        <v>11.66361260414124</v>
+        <v>10.9492564201355</v>
       </c>
       <c r="I8" t="n">
-        <v>16.15394496917725</v>
+        <v>11.54808020591736</v>
       </c>
       <c r="J8" t="n">
-        <v>11.26070809364319</v>
+        <v>11.91220545768738</v>
       </c>
       <c r="K8" t="n">
-        <v>11.88963079452515</v>
+        <v>11.80889630317688</v>
       </c>
       <c r="L8" t="n">
-        <v>13.11766169071197</v>
+        <v>11.81040799617767</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98041749000549</v>
+        <v>15.25218677520752</v>
       </c>
       <c r="C9" t="n">
-        <v>10.72213912010193</v>
+        <v>11.83083033561707</v>
       </c>
       <c r="D9" t="n">
-        <v>10.89614129066467</v>
+        <v>10.52270221710205</v>
       </c>
       <c r="E9" t="n">
-        <v>10.46136021614075</v>
+        <v>12.13064408302307</v>
       </c>
       <c r="F9" t="n">
-        <v>10.00748777389526</v>
+        <v>11.46332144737244</v>
       </c>
       <c r="G9" t="n">
-        <v>12.03470468521118</v>
+        <v>12.01089119911194</v>
       </c>
       <c r="H9" t="n">
-        <v>11.72501921653748</v>
+        <v>13.21631693840027</v>
       </c>
       <c r="I9" t="n">
-        <v>10.63807201385498</v>
+        <v>12.56203103065491</v>
       </c>
       <c r="J9" t="n">
-        <v>10.57755589485168</v>
+        <v>17.31803965568542</v>
       </c>
       <c r="K9" t="n">
-        <v>10.40253567695618</v>
+        <v>13.89755058288574</v>
       </c>
       <c r="L9" t="n">
-        <v>10.84454333782196</v>
+        <v>13.02045142650604</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>11.86982011795044</v>
+        <v>12.66408777236938</v>
       </c>
       <c r="C10" t="n">
-        <v>11.77802109718323</v>
+        <v>12.25762343406677</v>
       </c>
       <c r="D10" t="n">
-        <v>12.03736591339111</v>
+        <v>12.72047543525696</v>
       </c>
       <c r="E10" t="n">
-        <v>12.79241466522217</v>
+        <v>11.59185171127319</v>
       </c>
       <c r="F10" t="n">
-        <v>12.00992107391357</v>
+        <v>12.0591869354248</v>
       </c>
       <c r="G10" t="n">
-        <v>15.36386275291443</v>
+        <v>12.09654784202576</v>
       </c>
       <c r="H10" t="n">
-        <v>11.85385060310364</v>
+        <v>12.95431995391846</v>
       </c>
       <c r="I10" t="n">
-        <v>10.857346534729</v>
+        <v>11.68004989624023</v>
       </c>
       <c r="J10" t="n">
-        <v>12.40541529655457</v>
+        <v>12.25575804710388</v>
       </c>
       <c r="K10" t="n">
-        <v>11.83385467529297</v>
+        <v>12.81340098381042</v>
       </c>
       <c r="L10" t="n">
-        <v>12.28018727302551</v>
+        <v>12.30933020114899</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>11.44537925720215</v>
+        <v>12.9669783115387</v>
       </c>
       <c r="C11" t="n">
-        <v>15.37634778022766</v>
+        <v>12.2328200340271</v>
       </c>
       <c r="D11" t="n">
-        <v>11.75955629348755</v>
+        <v>12.76996541023254</v>
       </c>
       <c r="E11" t="n">
-        <v>12.35206413269043</v>
+        <v>16.13638091087341</v>
       </c>
       <c r="F11" t="n">
-        <v>14.00830340385437</v>
+        <v>13.59239029884338</v>
       </c>
       <c r="G11" t="n">
-        <v>12.10474753379822</v>
+        <v>11.84181237220764</v>
       </c>
       <c r="H11" t="n">
-        <v>11.84719395637512</v>
+        <v>12.80042290687561</v>
       </c>
       <c r="I11" t="n">
-        <v>11.44022750854492</v>
+        <v>12.41638135910034</v>
       </c>
       <c r="J11" t="n">
-        <v>11.45472359657288</v>
+        <v>12.13159251213074</v>
       </c>
       <c r="K11" t="n">
-        <v>10.75055742263794</v>
+        <v>11.333651304245</v>
       </c>
       <c r="L11" t="n">
-        <v>12.25391008853912</v>
+        <v>12.82223954200745</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>13.88592338562012</v>
+        <v>12.01976084709167</v>
       </c>
       <c r="C12" t="n">
-        <v>11.64722108840942</v>
+        <v>14.11785483360291</v>
       </c>
       <c r="D12" t="n">
-        <v>12.14590525627136</v>
+        <v>12.59473443031311</v>
       </c>
       <c r="E12" t="n">
-        <v>12.29183077812195</v>
+        <v>14.61296653747559</v>
       </c>
       <c r="F12" t="n">
-        <v>15.470290184021</v>
+        <v>15.36812019348145</v>
       </c>
       <c r="G12" t="n">
-        <v>12.09952902793884</v>
+        <v>14.50507616996765</v>
       </c>
       <c r="H12" t="n">
-        <v>11.26127076148987</v>
+        <v>11.75308084487915</v>
       </c>
       <c r="I12" t="n">
-        <v>16.71603012084961</v>
+        <v>12.07923460006714</v>
       </c>
       <c r="J12" t="n">
-        <v>16.9078004360199</v>
+        <v>15.36833333969116</v>
       </c>
       <c r="K12" t="n">
-        <v>13.2727530002594</v>
+        <v>13.00785183906555</v>
       </c>
       <c r="L12" t="n">
-        <v>13.56985540390015</v>
+        <v>13.54270136356354</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>16.35632586479187</v>
+        <v>13.19240760803223</v>
       </c>
       <c r="C13" t="n">
-        <v>16.52483987808228</v>
+        <v>13.23929166793823</v>
       </c>
       <c r="D13" t="n">
-        <v>13.97097706794739</v>
+        <v>16.41033339500427</v>
       </c>
       <c r="E13" t="n">
-        <v>13.859947681427</v>
+        <v>15.48669719696045</v>
       </c>
       <c r="F13" t="n">
-        <v>14.810471534729</v>
+        <v>16.04426026344299</v>
       </c>
       <c r="G13" t="n">
-        <v>14.42252159118652</v>
+        <v>16.61972641944885</v>
       </c>
       <c r="H13" t="n">
-        <v>13.70133876800537</v>
+        <v>13.2769935131073</v>
       </c>
       <c r="I13" t="n">
-        <v>18.11142683029175</v>
+        <v>15.89567589759827</v>
       </c>
       <c r="J13" t="n">
-        <v>12.56381916999817</v>
+        <v>13.18569183349609</v>
       </c>
       <c r="K13" t="n">
-        <v>13.08841753005981</v>
+        <v>12.6161630153656</v>
       </c>
       <c r="L13" t="n">
-        <v>14.74100859165192</v>
+        <v>14.59672408103943</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>10.860764503479</v>
+        <v>12.43964505195618</v>
       </c>
       <c r="C14" t="n">
-        <v>11.70707130432129</v>
+        <v>11.76290416717529</v>
       </c>
       <c r="D14" t="n">
-        <v>11.85826110839844</v>
+        <v>11.48660087585449</v>
       </c>
       <c r="E14" t="n">
-        <v>16.3104043006897</v>
+        <v>13.08496308326721</v>
       </c>
       <c r="F14" t="n">
-        <v>10.95711350440979</v>
+        <v>12.32841944694519</v>
       </c>
       <c r="G14" t="n">
-        <v>11.35280847549438</v>
+        <v>12.43366980552673</v>
       </c>
       <c r="H14" t="n">
-        <v>15.8975248336792</v>
+        <v>11.00774931907654</v>
       </c>
       <c r="I14" t="n">
-        <v>15.71051073074341</v>
+        <v>12.6477746963501</v>
       </c>
       <c r="J14" t="n">
-        <v>11.51522541046143</v>
+        <v>13.0949981212616</v>
       </c>
       <c r="K14" t="n">
-        <v>12.43734693527222</v>
+        <v>11.78501844406128</v>
       </c>
       <c r="L14" t="n">
-        <v>12.86070311069489</v>
+        <v>12.20717430114746</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>16.51842498779297</v>
+        <v>13.89126682281494</v>
       </c>
       <c r="C15" t="n">
-        <v>11.26132559776306</v>
+        <v>11.96886110305786</v>
       </c>
       <c r="D15" t="n">
-        <v>12.65229082107544</v>
+        <v>13.14558434486389</v>
       </c>
       <c r="E15" t="n">
-        <v>11.8807532787323</v>
+        <v>11.99894881248474</v>
       </c>
       <c r="F15" t="n">
-        <v>11.27377343177795</v>
+        <v>13.18838024139404</v>
       </c>
       <c r="G15" t="n">
-        <v>10.85533833503723</v>
+        <v>14.34592723846436</v>
       </c>
       <c r="H15" t="n">
-        <v>10.83338904380798</v>
+        <v>13.25323748588562</v>
       </c>
       <c r="I15" t="n">
-        <v>11.61141085624695</v>
+        <v>12.61588549613953</v>
       </c>
       <c r="J15" t="n">
-        <v>11.23938298225403</v>
+        <v>11.05087232589722</v>
       </c>
       <c r="K15" t="n">
-        <v>12.15450716018677</v>
+        <v>12.27623105049133</v>
       </c>
       <c r="L15" t="n">
-        <v>12.02805964946747</v>
+        <v>12.77351949214935</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>11.09825325012207</v>
+        <v>11.12514996528625</v>
       </c>
       <c r="C16" t="n">
-        <v>11.39521932601929</v>
+        <v>12.03748536109924</v>
       </c>
       <c r="D16" t="n">
-        <v>11.34200096130371</v>
+        <v>12.6782398223877</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5803689956665</v>
+        <v>12.16550040245056</v>
       </c>
       <c r="F16" t="n">
-        <v>11.42925691604614</v>
+        <v>12.12750172615051</v>
       </c>
       <c r="G16" t="n">
-        <v>10.59340834617615</v>
+        <v>13.4420177936554</v>
       </c>
       <c r="H16" t="n">
-        <v>11.32307481765747</v>
+        <v>11.79428958892822</v>
       </c>
       <c r="I16" t="n">
-        <v>11.11457872390747</v>
+        <v>13.80708599090576</v>
       </c>
       <c r="J16" t="n">
-        <v>12.78324437141418</v>
+        <v>12.669020652771</v>
       </c>
       <c r="K16" t="n">
-        <v>11.19191789627075</v>
+        <v>13.86191916465759</v>
       </c>
       <c r="L16" t="n">
-        <v>11.38513236045837</v>
+        <v>12.57082104682922</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>10.77094054222107</v>
+        <v>11.01285552978516</v>
       </c>
       <c r="C17" t="n">
-        <v>11.77888822555542</v>
+        <v>11.48460865020752</v>
       </c>
       <c r="D17" t="n">
-        <v>11.80962705612183</v>
+        <v>11.47268605232239</v>
       </c>
       <c r="E17" t="n">
-        <v>12.90168619155884</v>
+        <v>12.05765342712402</v>
       </c>
       <c r="F17" t="n">
-        <v>11.28325343132019</v>
+        <v>15.39841079711914</v>
       </c>
       <c r="G17" t="n">
-        <v>12.32111525535583</v>
+        <v>12.3024582862854</v>
       </c>
       <c r="H17" t="n">
-        <v>11.51919054985046</v>
+        <v>11.96393060684204</v>
       </c>
       <c r="I17" t="n">
-        <v>12.04436421394348</v>
+        <v>11.34796071052551</v>
       </c>
       <c r="J17" t="n">
-        <v>10.79249906539917</v>
+        <v>12.18186140060425</v>
       </c>
       <c r="K17" t="n">
-        <v>12.0812075138092</v>
+        <v>12.29152965545654</v>
       </c>
       <c r="L17" t="n">
-        <v>11.73027720451355</v>
+        <v>12.1513955116272</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>11.64731812477112</v>
+        <v>11.55690336227417</v>
       </c>
       <c r="C18" t="n">
-        <v>13.28964614868164</v>
+        <v>14.29838585853577</v>
       </c>
       <c r="D18" t="n">
-        <v>10.73514199256897</v>
+        <v>15.15388655662537</v>
       </c>
       <c r="E18" t="n">
-        <v>13.81432318687439</v>
+        <v>12.55801367759705</v>
       </c>
       <c r="F18" t="n">
-        <v>14.08164739608765</v>
+        <v>15.45758128166199</v>
       </c>
       <c r="G18" t="n">
-        <v>11.57200574874878</v>
+        <v>11.48471593856812</v>
       </c>
       <c r="H18" t="n">
-        <v>12.26330375671387</v>
+        <v>12.74456810951233</v>
       </c>
       <c r="I18" t="n">
-        <v>11.30718731880188</v>
+        <v>13.35247397422791</v>
       </c>
       <c r="J18" t="n">
-        <v>11.57260799407959</v>
+        <v>11.58605623245239</v>
       </c>
       <c r="K18" t="n">
-        <v>13.38839817047119</v>
+        <v>14.99779939651489</v>
       </c>
       <c r="L18" t="n">
-        <v>12.36715798377991</v>
+        <v>13.319038438797</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>17.16076850891113</v>
+        <v>11.78002095222473</v>
       </c>
       <c r="C19" t="n">
-        <v>14.10412049293518</v>
+        <v>16.71241402626038</v>
       </c>
       <c r="D19" t="n">
-        <v>12.14903855323792</v>
+        <v>16.73283338546753</v>
       </c>
       <c r="E19" t="n">
-        <v>11.10771632194519</v>
+        <v>16.548344373703</v>
       </c>
       <c r="F19" t="n">
-        <v>11.74308443069458</v>
+        <v>15.0153820514679</v>
       </c>
       <c r="G19" t="n">
-        <v>15.01827955245972</v>
+        <v>13.19371128082275</v>
       </c>
       <c r="H19" t="n">
-        <v>14.34195685386658</v>
+        <v>12.9837954044342</v>
       </c>
       <c r="I19" t="n">
-        <v>15.95383882522583</v>
+        <v>14.60257935523987</v>
       </c>
       <c r="J19" t="n">
-        <v>11.6697986125946</v>
+        <v>12.24277663230896</v>
       </c>
       <c r="K19" t="n">
-        <v>15.07509708404541</v>
+        <v>12.79538989067078</v>
       </c>
       <c r="L19" t="n">
-        <v>13.83236992359161</v>
+        <v>14.26072473526001</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>9.990530252456665</v>
+        <v>11.21342134475708</v>
       </c>
       <c r="C20" t="n">
-        <v>10.2389132976532</v>
+        <v>10.67830014228821</v>
       </c>
       <c r="D20" t="n">
-        <v>10.69529676437378</v>
+        <v>11.49168634414673</v>
       </c>
       <c r="E20" t="n">
-        <v>14.18722558021545</v>
+        <v>11.353102684021</v>
       </c>
       <c r="F20" t="n">
-        <v>10.71362566947937</v>
+        <v>11.08082962036133</v>
       </c>
       <c r="G20" t="n">
-        <v>11.06920170783997</v>
+        <v>10.71123385429382</v>
       </c>
       <c r="H20" t="n">
-        <v>10.66872501373291</v>
+        <v>11.6314685344696</v>
       </c>
       <c r="I20" t="n">
-        <v>12.89396476745605</v>
+        <v>14.58986949920654</v>
       </c>
       <c r="J20" t="n">
-        <v>10.10570406913757</v>
+        <v>18.99982619285583</v>
       </c>
       <c r="K20" t="n">
-        <v>10.21440100669861</v>
+        <v>11.49556851387024</v>
       </c>
       <c r="L20" t="n">
-        <v>11.07775881290436</v>
+        <v>12.32453067302704</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>11.87063264846802</v>
+        <v>12.50098776817322</v>
       </c>
       <c r="C21" t="n">
-        <v>10.71239376068115</v>
+        <v>13.81727290153503</v>
       </c>
       <c r="D21" t="n">
-        <v>11.48871564865112</v>
+        <v>12.85925006866455</v>
       </c>
       <c r="E21" t="n">
-        <v>11.30470132827759</v>
+        <v>11.7695038318634</v>
       </c>
       <c r="F21" t="n">
-        <v>11.54911470413208</v>
+        <v>11.07727956771851</v>
       </c>
       <c r="G21" t="n">
-        <v>13.45924925804138</v>
+        <v>11.60843515396118</v>
       </c>
       <c r="H21" t="n">
-        <v>10.27780866622925</v>
+        <v>10.95757365226746</v>
       </c>
       <c r="I21" t="n">
-        <v>14.63172173500061</v>
+        <v>12.04232335090637</v>
       </c>
       <c r="J21" t="n">
-        <v>13.78992295265198</v>
+        <v>11.22144031524658</v>
       </c>
       <c r="K21" t="n">
-        <v>11.38747787475586</v>
+        <v>11.59745168685913</v>
       </c>
       <c r="L21" t="n">
-        <v>12.0471738576889</v>
+        <v>11.94515182971954</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>11.14067196846008</v>
+        <v>13.73548913002014</v>
       </c>
       <c r="C22" t="n">
-        <v>14.09905481338501</v>
+        <v>17.58765339851379</v>
       </c>
       <c r="D22" t="n">
-        <v>11.96551418304443</v>
+        <v>13.19837808609009</v>
       </c>
       <c r="E22" t="n">
-        <v>12.87319922447205</v>
+        <v>11.77599000930786</v>
       </c>
       <c r="F22" t="n">
-        <v>14.89001274108887</v>
+        <v>11.4906895160675</v>
       </c>
       <c r="G22" t="n">
-        <v>10.59404945373535</v>
+        <v>11.47693991661072</v>
       </c>
       <c r="H22" t="n">
-        <v>13.38866877555847</v>
+        <v>12.34900522232056</v>
       </c>
       <c r="I22" t="n">
-        <v>10.82381987571716</v>
+        <v>11.88720536231995</v>
       </c>
       <c r="J22" t="n">
-        <v>16.11006021499634</v>
+        <v>11.98597431182861</v>
       </c>
       <c r="K22" t="n">
-        <v>14.88280606269836</v>
+        <v>14.76192450523376</v>
       </c>
       <c r="L22" t="n">
-        <v>13.07678573131561</v>
+        <v>13.0249249458313</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>13.00814151763916</v>
+        <v>12.75101351737976</v>
       </c>
       <c r="C23" t="n">
-        <v>10.29622650146484</v>
+        <v>16.10346746444702</v>
       </c>
       <c r="D23" t="n">
-        <v>10.99341487884521</v>
+        <v>11.98645877838135</v>
       </c>
       <c r="E23" t="n">
-        <v>12.42963552474976</v>
+        <v>11.87875151634216</v>
       </c>
       <c r="F23" t="n">
-        <v>11.50757932662964</v>
+        <v>10.74388647079468</v>
       </c>
       <c r="G23" t="n">
-        <v>10.56700992584229</v>
+        <v>11.24922251701355</v>
       </c>
       <c r="H23" t="n">
-        <v>10.96046876907349</v>
+        <v>11.73497462272644</v>
       </c>
       <c r="I23" t="n">
-        <v>11.15946745872498</v>
+        <v>11.10912489891052</v>
       </c>
       <c r="J23" t="n">
-        <v>11.14696383476257</v>
+        <v>14.23298811912537</v>
       </c>
       <c r="K23" t="n">
-        <v>13.84599542617798</v>
+        <v>11.5544605255127</v>
       </c>
       <c r="L23" t="n">
-        <v>11.59149031639099</v>
+        <v>12.33443484306335</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>11.3509829044342</v>
+        <v>16.72450160980225</v>
       </c>
       <c r="C24" t="n">
-        <v>14.17459440231323</v>
+        <v>11.52650380134583</v>
       </c>
       <c r="D24" t="n">
-        <v>11.03232264518738</v>
+        <v>13.31642746925354</v>
       </c>
       <c r="E24" t="n">
-        <v>15.80385255813599</v>
+        <v>14.48067760467529</v>
       </c>
       <c r="F24" t="n">
-        <v>13.51235389709473</v>
+        <v>12.94152426719666</v>
       </c>
       <c r="G24" t="n">
-        <v>19.51973271369934</v>
+        <v>12.43235874176025</v>
       </c>
       <c r="H24" t="n">
-        <v>17.16877412796021</v>
+        <v>17.78164076805115</v>
       </c>
       <c r="I24" t="n">
-        <v>15.22432804107666</v>
+        <v>12.90451693534851</v>
       </c>
       <c r="J24" t="n">
-        <v>17.13690376281738</v>
+        <v>14.95986747741699</v>
       </c>
       <c r="K24" t="n">
-        <v>12.91291856765747</v>
+        <v>12.25262808799744</v>
       </c>
       <c r="L24" t="n">
-        <v>14.78367636203766</v>
+        <v>13.93206467628479</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>13.26850533485413</v>
+        <v>18.39909434318542</v>
       </c>
       <c r="C25" t="n">
-        <v>18.07893753051758</v>
+        <v>17.59388518333435</v>
       </c>
       <c r="D25" t="n">
-        <v>15.53908705711365</v>
+        <v>20.81784653663635</v>
       </c>
       <c r="E25" t="n">
-        <v>13.75924611091614</v>
+        <v>17.89647221565247</v>
       </c>
       <c r="F25" t="n">
-        <v>13.80361223220825</v>
+        <v>19.00661396980286</v>
       </c>
       <c r="G25" t="n">
-        <v>13.49542760848999</v>
+        <v>15.83912825584412</v>
       </c>
       <c r="H25" t="n">
-        <v>17.7012984752655</v>
+        <v>19.05992937088013</v>
       </c>
       <c r="I25" t="n">
-        <v>17.27404689788818</v>
+        <v>14.28136730194092</v>
       </c>
       <c r="J25" t="n">
-        <v>16.93946814537048</v>
+        <v>16.30631160736084</v>
       </c>
       <c r="K25" t="n">
-        <v>18.07301330566406</v>
+        <v>18.57031917572021</v>
       </c>
       <c r="L25" t="n">
-        <v>15.7932642698288</v>
+        <v>17.77709679603577</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>10.25781583786011</v>
+        <v>11.49045324325562</v>
       </c>
       <c r="C26" t="n">
-        <v>10.71564340591431</v>
+        <v>9.808491945266724</v>
       </c>
       <c r="D26" t="n">
-        <v>10.68921542167664</v>
+        <v>11.14604520797729</v>
       </c>
       <c r="E26" t="n">
-        <v>9.423500061035156</v>
+        <v>9.651447057723999</v>
       </c>
       <c r="F26" t="n">
-        <v>9.775616884231567</v>
+        <v>10.16209816932678</v>
       </c>
       <c r="G26" t="n">
-        <v>10.60245394706726</v>
+        <v>10.90353083610535</v>
       </c>
       <c r="H26" t="n">
-        <v>10.62236714363098</v>
+        <v>11.10718536376953</v>
       </c>
       <c r="I26" t="n">
-        <v>10.39146661758423</v>
+        <v>10.25292444229126</v>
       </c>
       <c r="J26" t="n">
-        <v>11.78637909889221</v>
+        <v>12.24035930633545</v>
       </c>
       <c r="K26" t="n">
-        <v>11.47716355323792</v>
+        <v>11.04261422157288</v>
       </c>
       <c r="L26" t="n">
-        <v>10.57416219711304</v>
+        <v>10.78051497936249</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>15.46976613998413</v>
+        <v>17.94044041633606</v>
       </c>
       <c r="C27" t="n">
-        <v>11.83517932891846</v>
+        <v>14.45837044715881</v>
       </c>
       <c r="D27" t="n">
-        <v>12.49005579948425</v>
+        <v>14.02206110954285</v>
       </c>
       <c r="E27" t="n">
-        <v>12.05086708068848</v>
+        <v>17.23684811592102</v>
       </c>
       <c r="F27" t="n">
-        <v>12.27171182632446</v>
+        <v>12.21675658226013</v>
       </c>
       <c r="G27" t="n">
-        <v>12.4164776802063</v>
+        <v>14.20289778709412</v>
       </c>
       <c r="H27" t="n">
-        <v>18.01407885551453</v>
+        <v>13.45898962020874</v>
       </c>
       <c r="I27" t="n">
-        <v>16.04609656333923</v>
+        <v>17.57849454879761</v>
       </c>
       <c r="J27" t="n">
-        <v>12.51758170127869</v>
+        <v>13.64654970169067</v>
       </c>
       <c r="K27" t="n">
-        <v>12.50015115737915</v>
+        <v>14.88546872138977</v>
       </c>
       <c r="L27" t="n">
-        <v>13.56119661331177</v>
+        <v>14.96468770503998</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>11.19301128387451</v>
+        <v>13.49253749847412</v>
       </c>
       <c r="C28" t="n">
-        <v>11.16157150268555</v>
+        <v>11.55525732040405</v>
       </c>
       <c r="D28" t="n">
-        <v>11.12118887901306</v>
+        <v>12.43879342079163</v>
       </c>
       <c r="E28" t="n">
-        <v>12.1346001625061</v>
+        <v>16.66181540489197</v>
       </c>
       <c r="F28" t="n">
-        <v>10.7361319065094</v>
+        <v>12.30664849281311</v>
       </c>
       <c r="G28" t="n">
-        <v>10.85337162017822</v>
+        <v>12.09871530532837</v>
       </c>
       <c r="H28" t="n">
-        <v>11.07330751419067</v>
+        <v>14.33534407615662</v>
       </c>
       <c r="I28" t="n">
-        <v>11.32588362693787</v>
+        <v>11.93606734275818</v>
       </c>
       <c r="J28" t="n">
-        <v>11.48116040229797</v>
+        <v>11.95043563842773</v>
       </c>
       <c r="K28" t="n">
-        <v>10.80088496208191</v>
+        <v>11.22186660766602</v>
       </c>
       <c r="L28" t="n">
-        <v>11.18811118602753</v>
+        <v>12.79974811077118</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>11.35796022415161</v>
+        <v>14.46038293838501</v>
       </c>
       <c r="C29" t="n">
-        <v>10.76100158691406</v>
+        <v>12.4987165927887</v>
       </c>
       <c r="D29" t="n">
-        <v>10.22641468048096</v>
+        <v>14.84825396537781</v>
       </c>
       <c r="E29" t="n">
-        <v>10.47776699066162</v>
+        <v>9.948662519454956</v>
       </c>
       <c r="F29" t="n">
-        <v>10.5869882106781</v>
+        <v>11.34456586837769</v>
       </c>
       <c r="G29" t="n">
-        <v>11.50720834732056</v>
+        <v>13.70111608505249</v>
       </c>
       <c r="H29" t="n">
-        <v>10.05541968345642</v>
+        <v>13.62025570869446</v>
       </c>
       <c r="I29" t="n">
-        <v>11.89269542694092</v>
+        <v>12.45775938034058</v>
       </c>
       <c r="J29" t="n">
-        <v>11.24087595939636</v>
+        <v>16.12723779678345</v>
       </c>
       <c r="K29" t="n">
-        <v>10.3700897693634</v>
+        <v>11.56030631065369</v>
       </c>
       <c r="L29" t="n">
-        <v>10.8476420879364</v>
+        <v>13.05672571659088</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>11.15561509132385</v>
+        <v>15.43419194221497</v>
       </c>
       <c r="C30" t="n">
-        <v>11.78946018218994</v>
+        <v>14.0991222858429</v>
       </c>
       <c r="D30" t="n">
-        <v>10.72221207618713</v>
+        <v>14.05267405509949</v>
       </c>
       <c r="E30" t="n">
-        <v>10.72818183898926</v>
+        <v>12.8034040927887</v>
       </c>
       <c r="F30" t="n">
-        <v>13.2802107334137</v>
+        <v>13.43320870399475</v>
       </c>
       <c r="G30" t="n">
-        <v>12.71706366539001</v>
+        <v>14.91218900680542</v>
       </c>
       <c r="H30" t="n">
-        <v>14.34296441078186</v>
+        <v>13.77769231796265</v>
       </c>
       <c r="I30" t="n">
-        <v>12.92686128616333</v>
+        <v>14.0849392414093</v>
       </c>
       <c r="J30" t="n">
-        <v>12.04165244102478</v>
+        <v>12.52308750152588</v>
       </c>
       <c r="K30" t="n">
-        <v>14.23200058937073</v>
+        <v>13.67081046104431</v>
       </c>
       <c r="L30" t="n">
-        <v>12.39362223148346</v>
+        <v>13.87913196086884</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>12.00875854492188</v>
+        <v>16.23756694793701</v>
       </c>
       <c r="C31" t="n">
-        <v>14.19956636428833</v>
+        <v>20.94226574897766</v>
       </c>
       <c r="D31" t="n">
-        <v>10.83182072639465</v>
+        <v>15.06210017204285</v>
       </c>
       <c r="E31" t="n">
-        <v>14.54270672798157</v>
+        <v>17.42051720619202</v>
       </c>
       <c r="F31" t="n">
-        <v>16.66616678237915</v>
+        <v>16.48044919967651</v>
       </c>
       <c r="G31" t="n">
-        <v>11.63771295547485</v>
+        <v>20.01357626914978</v>
       </c>
       <c r="H31" t="n">
-        <v>14.69575595855713</v>
+        <v>12.1668107509613</v>
       </c>
       <c r="I31" t="n">
-        <v>14.42645311355591</v>
+        <v>17.72778511047363</v>
       </c>
       <c r="J31" t="n">
-        <v>12.61015629768372</v>
+        <v>12.20332479476929</v>
       </c>
       <c r="K31" t="n">
-        <v>16.109623670578</v>
+        <v>16.08666229248047</v>
       </c>
       <c r="L31" t="n">
-        <v>13.77287211418152</v>
+        <v>16.43410584926605</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>12.31849908828735</v>
+        <v>12.66083455085754</v>
       </c>
       <c r="C32" t="n">
-        <v>11.43926024436951</v>
+        <v>11.46018147468567</v>
       </c>
       <c r="D32" t="n">
-        <v>14.34318828582764</v>
+        <v>16.61527180671692</v>
       </c>
       <c r="E32" t="n">
-        <v>11.40333390235901</v>
+        <v>11.45449209213257</v>
       </c>
       <c r="F32" t="n">
-        <v>13.13135480880737</v>
+        <v>11.7472038269043</v>
       </c>
       <c r="G32" t="n">
-        <v>13.27547359466553</v>
+        <v>11.35425567626953</v>
       </c>
       <c r="H32" t="n">
-        <v>17.25017356872559</v>
+        <v>12.11699151992798</v>
       </c>
       <c r="I32" t="n">
-        <v>10.71546411514282</v>
+        <v>13.80070686340332</v>
       </c>
       <c r="J32" t="n">
-        <v>11.71965003013611</v>
+        <v>11.38695478439331</v>
       </c>
       <c r="K32" t="n">
-        <v>10.24943447113037</v>
+        <v>13.26560807228088</v>
       </c>
       <c r="L32" t="n">
-        <v>12.58458321094513</v>
+        <v>12.5862500667572</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>11.33864879608154</v>
+        <v>12.11568808555603</v>
       </c>
       <c r="C33" t="n">
-        <v>12.18743538856506</v>
+        <v>15.17810773849487</v>
       </c>
       <c r="D33" t="n">
-        <v>13.36194658279419</v>
+        <v>11.73410034179688</v>
       </c>
       <c r="E33" t="n">
-        <v>12.03236603736877</v>
+        <v>11.45004916191101</v>
       </c>
       <c r="F33" t="n">
-        <v>14.80875277519226</v>
+        <v>12.69272971153259</v>
       </c>
       <c r="G33" t="n">
-        <v>11.66679906845093</v>
+        <v>12.81575059890747</v>
       </c>
       <c r="H33" t="n">
-        <v>12.80644536018372</v>
+        <v>12.62661695480347</v>
       </c>
       <c r="I33" t="n">
-        <v>11.42139911651611</v>
+        <v>16.23991203308105</v>
       </c>
       <c r="J33" t="n">
-        <v>13.31613731384277</v>
+        <v>16.69919490814209</v>
       </c>
       <c r="K33" t="n">
-        <v>12.70945858955383</v>
+        <v>12.43572878837585</v>
       </c>
       <c r="L33" t="n">
-        <v>12.56493890285492</v>
+        <v>13.39878783226013</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>10.98947215080261</v>
+        <v>10.75794553756714</v>
       </c>
       <c r="C34" t="n">
-        <v>11.10959601402283</v>
+        <v>11.27017259597778</v>
       </c>
       <c r="D34" t="n">
-        <v>10.82487344741821</v>
+        <v>11.26129126548767</v>
       </c>
       <c r="E34" t="n">
-        <v>11.66172623634338</v>
+        <v>11.55758118629456</v>
       </c>
       <c r="F34" t="n">
-        <v>11.08815407752991</v>
+        <v>10.96948027610779</v>
       </c>
       <c r="G34" t="n">
-        <v>10.37102699279785</v>
+        <v>10.7778058052063</v>
       </c>
       <c r="H34" t="n">
-        <v>12.45752620697021</v>
+        <v>11.28406119346619</v>
       </c>
       <c r="I34" t="n">
-        <v>14.74098968505859</v>
+        <v>11.06721305847168</v>
       </c>
       <c r="J34" t="n">
-        <v>12.52471971511841</v>
+        <v>10.49885773658752</v>
       </c>
       <c r="K34" t="n">
-        <v>11.28117156028748</v>
+        <v>13.27361869812012</v>
       </c>
       <c r="L34" t="n">
-        <v>11.70492560863495</v>
+        <v>11.27180273532867</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>11.95935726165771</v>
+        <v>13.23576045036316</v>
       </c>
       <c r="C35" t="n">
-        <v>11.1096088886261</v>
+        <v>12.69194173812866</v>
       </c>
       <c r="D35" t="n">
-        <v>12.28055548667908</v>
+        <v>11.13671588897705</v>
       </c>
       <c r="E35" t="n">
-        <v>12.78682494163513</v>
+        <v>11.88146281242371</v>
       </c>
       <c r="F35" t="n">
-        <v>10.85532140731812</v>
+        <v>12.05386090278625</v>
       </c>
       <c r="G35" t="n">
-        <v>11.4354305267334</v>
+        <v>13.75455570220947</v>
       </c>
       <c r="H35" t="n">
-        <v>11.91063547134399</v>
+        <v>14.26984357833862</v>
       </c>
       <c r="I35" t="n">
-        <v>14.66415500640869</v>
+        <v>11.39653277397156</v>
       </c>
       <c r="J35" t="n">
-        <v>12.36796474456787</v>
+        <v>12.22900867462158</v>
       </c>
       <c r="K35" t="n">
-        <v>10.57060503959656</v>
+        <v>11.56598663330078</v>
       </c>
       <c r="L35" t="n">
-        <v>11.99404587745667</v>
+        <v>12.42156691551208</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>11.53413033485413</v>
+        <v>13.2691969871521</v>
       </c>
       <c r="C36" t="n">
-        <v>13.05077838897705</v>
+        <v>11.7176399230957</v>
       </c>
       <c r="D36" t="n">
-        <v>12.00053977966309</v>
+        <v>11.55156636238098</v>
       </c>
       <c r="E36" t="n">
-        <v>13.55830764770508</v>
+        <v>13.82749700546265</v>
       </c>
       <c r="F36" t="n">
-        <v>10.72159910202026</v>
+        <v>13.17202305793762</v>
       </c>
       <c r="G36" t="n">
-        <v>12.27805066108704</v>
+        <v>11.43826603889465</v>
       </c>
       <c r="H36" t="n">
-        <v>13.19965195655823</v>
+        <v>13.7137086391449</v>
       </c>
       <c r="I36" t="n">
-        <v>10.91210198402405</v>
+        <v>11.93428540229797</v>
       </c>
       <c r="J36" t="n">
-        <v>13.52039742469788</v>
+        <v>12.46465539932251</v>
       </c>
       <c r="K36" t="n">
-        <v>13.45998620986938</v>
+        <v>19.62768602371216</v>
       </c>
       <c r="L36" t="n">
-        <v>12.42355434894562</v>
+        <v>13.27165248394012</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>11.19397974014282</v>
+        <v>11.54315328598022</v>
       </c>
       <c r="C37" t="n">
-        <v>9.603542566299438</v>
+        <v>13.04783225059509</v>
       </c>
       <c r="D37" t="n">
-        <v>10.8064591884613</v>
+        <v>11.98874688148499</v>
       </c>
       <c r="E37" t="n">
-        <v>12.26177787780762</v>
+        <v>13.20555877685547</v>
       </c>
       <c r="F37" t="n">
-        <v>12.28020286560059</v>
+        <v>12.67010736465454</v>
       </c>
       <c r="G37" t="n">
-        <v>10.69325709342957</v>
+        <v>12.62545990943909</v>
       </c>
       <c r="H37" t="n">
-        <v>14.9099702835083</v>
+        <v>12.82640147209167</v>
       </c>
       <c r="I37" t="n">
-        <v>11.06334376335144</v>
+        <v>11.38275480270386</v>
       </c>
       <c r="J37" t="n">
-        <v>16.58122277259827</v>
+        <v>11.23641395568848</v>
       </c>
       <c r="K37" t="n">
-        <v>10.42945098876953</v>
+        <v>11.05088663101196</v>
       </c>
       <c r="L37" t="n">
-        <v>11.98232071399689</v>
+        <v>12.15773153305054</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>11.97949433326721</v>
+        <v>13.00352096557617</v>
       </c>
       <c r="C38" t="n">
-        <v>11.3147075176239</v>
+        <v>10.70463418960571</v>
       </c>
       <c r="D38" t="n">
-        <v>11.92707824707031</v>
+        <v>13.55531406402588</v>
       </c>
       <c r="E38" t="n">
-        <v>11.28825736045837</v>
+        <v>16.22908496856689</v>
       </c>
       <c r="F38" t="n">
-        <v>11.76801943778992</v>
+        <v>11.34642934799194</v>
       </c>
       <c r="G38" t="n">
-        <v>12.44828534126282</v>
+        <v>14.86852931976318</v>
       </c>
       <c r="H38" t="n">
-        <v>11.8049476146698</v>
+        <v>14.91405320167542</v>
       </c>
       <c r="I38" t="n">
-        <v>11.46877479553223</v>
+        <v>12.5693302154541</v>
       </c>
       <c r="J38" t="n">
-        <v>11.70573163032532</v>
+        <v>12.04943585395813</v>
       </c>
       <c r="K38" t="n">
-        <v>11.2812602519989</v>
+        <v>13.91653895378113</v>
       </c>
       <c r="L38" t="n">
-        <v>11.69865565299988</v>
+        <v>13.31568710803986</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>9.779144525527954</v>
+        <v>10.63144588470459</v>
       </c>
       <c r="C39" t="n">
-        <v>10.38255548477173</v>
+        <v>11.41646432876587</v>
       </c>
       <c r="D39" t="n">
-        <v>9.854898452758789</v>
+        <v>10.5604145526886</v>
       </c>
       <c r="E39" t="n">
-        <v>12.05528497695923</v>
+        <v>10.05644345283508</v>
       </c>
       <c r="F39" t="n">
-        <v>13.80690002441406</v>
+        <v>10.75551509857178</v>
       </c>
       <c r="G39" t="n">
-        <v>11.53014349937439</v>
+        <v>10.36408495903015</v>
       </c>
       <c r="H39" t="n">
-        <v>10.72723412513733</v>
+        <v>12.29152488708496</v>
       </c>
       <c r="I39" t="n">
-        <v>11.51916575431824</v>
+        <v>11.30317974090576</v>
       </c>
       <c r="J39" t="n">
-        <v>11.25733351707458</v>
+        <v>13.14387536048889</v>
       </c>
       <c r="K39" t="n">
-        <v>9.470407485961914</v>
+        <v>12.09840536117554</v>
       </c>
       <c r="L39" t="n">
-        <v>11.03830678462982</v>
+        <v>11.26213536262512</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>13.2312912940979</v>
+        <v>13.05599856376648</v>
       </c>
       <c r="C40" t="n">
-        <v>12.01038217544556</v>
+        <v>12.95600581169128</v>
       </c>
       <c r="D40" t="n">
-        <v>12.92305898666382</v>
+        <v>12.66997385025024</v>
       </c>
       <c r="E40" t="n">
-        <v>11.90120506286621</v>
+        <v>12.18233203887939</v>
       </c>
       <c r="F40" t="n">
-        <v>12.41509890556335</v>
+        <v>16.33928918838501</v>
       </c>
       <c r="G40" t="n">
-        <v>14.93451428413391</v>
+        <v>14.51341581344604</v>
       </c>
       <c r="H40" t="n">
-        <v>13.16307497024536</v>
+        <v>14.10852360725403</v>
       </c>
       <c r="I40" t="n">
-        <v>12.38841485977173</v>
+        <v>12.29254150390625</v>
       </c>
       <c r="J40" t="n">
-        <v>12.06431770324707</v>
+        <v>13.72694993019104</v>
       </c>
       <c r="K40" t="n">
-        <v>12.39146661758423</v>
+        <v>13.33074927330017</v>
       </c>
       <c r="L40" t="n">
-        <v>12.74228248596191</v>
+        <v>13.51757795810699</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>12.14857959747314</v>
+        <v>11.87464618682861</v>
       </c>
       <c r="C41" t="n">
-        <v>12.61289954185486</v>
+        <v>12.72659993171692</v>
       </c>
       <c r="D41" t="n">
-        <v>9.912261247634888</v>
+        <v>10.63763523101807</v>
       </c>
       <c r="E41" t="n">
-        <v>12.18950700759888</v>
+        <v>12.78540921211243</v>
       </c>
       <c r="F41" t="n">
-        <v>10.07088136672974</v>
+        <v>10.28693628311157</v>
       </c>
       <c r="G41" t="n">
-        <v>10.37704539299011</v>
+        <v>13.2341845035553</v>
       </c>
       <c r="H41" t="n">
-        <v>13.29164433479309</v>
+        <v>11.37921786308289</v>
       </c>
       <c r="I41" t="n">
-        <v>10.11478114128113</v>
+        <v>10.59423136711121</v>
       </c>
       <c r="J41" t="n">
-        <v>12.30617761611938</v>
+        <v>13.28372931480408</v>
       </c>
       <c r="K41" t="n">
-        <v>9.725750684738159</v>
+        <v>10.93058609962463</v>
       </c>
       <c r="L41" t="n">
-        <v>11.27495279312134</v>
+        <v>11.77331759929657</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>12.02738785743713</v>
+        <v>11.78231716156006</v>
       </c>
       <c r="C42" t="n">
-        <v>12.02933788299561</v>
+        <v>12.26314926147461</v>
       </c>
       <c r="D42" t="n">
-        <v>15.13893127441406</v>
+        <v>12.9675395488739</v>
       </c>
       <c r="E42" t="n">
-        <v>12.35306692123413</v>
+        <v>12.24433493614197</v>
       </c>
       <c r="F42" t="n">
-        <v>13.73551321029663</v>
+        <v>12.39073324203491</v>
       </c>
       <c r="G42" t="n">
-        <v>13.70860362052917</v>
+        <v>12.27749419212341</v>
       </c>
       <c r="H42" t="n">
-        <v>11.70564699172974</v>
+        <v>11.41614270210266</v>
       </c>
       <c r="I42" t="n">
-        <v>13.82884240150452</v>
+        <v>11.96466636657715</v>
       </c>
       <c r="J42" t="n">
-        <v>13.83092880249023</v>
+        <v>12.37088942527771</v>
       </c>
       <c r="K42" t="n">
-        <v>14.25797557830811</v>
+        <v>13.09247088432312</v>
       </c>
       <c r="L42" t="n">
-        <v>13.26162345409393</v>
+        <v>12.27697377204895</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>14.73626255989075</v>
+        <v>11.60813522338867</v>
       </c>
       <c r="C43" t="n">
-        <v>15.82518577575684</v>
+        <v>12.72554636001587</v>
       </c>
       <c r="D43" t="n">
-        <v>14.91007351875305</v>
+        <v>12.25108671188354</v>
       </c>
       <c r="E43" t="n">
-        <v>16.31173229217529</v>
+        <v>12.25368118286133</v>
       </c>
       <c r="F43" t="n">
-        <v>15.90328812599182</v>
+        <v>12.22354578971863</v>
       </c>
       <c r="G43" t="n">
-        <v>13.92304301261902</v>
+        <v>15.21499347686768</v>
       </c>
       <c r="H43" t="n">
-        <v>15.04918503761292</v>
+        <v>15.87753391265869</v>
       </c>
       <c r="I43" t="n">
-        <v>15.14540123939514</v>
+        <v>13.0238184928894</v>
       </c>
       <c r="J43" t="n">
-        <v>13.45456886291504</v>
+        <v>12.17816281318665</v>
       </c>
       <c r="K43" t="n">
-        <v>13.5228316783905</v>
+        <v>14.39140486717224</v>
       </c>
       <c r="L43" t="n">
-        <v>14.87815721035004</v>
+        <v>13.17479088306427</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>19.65059781074524</v>
+        <v>12.35953855514526</v>
       </c>
       <c r="C44" t="n">
-        <v>13.57795834541321</v>
+        <v>17.33913230895996</v>
       </c>
       <c r="D44" t="n">
-        <v>13.40653896331787</v>
+        <v>12.75855350494385</v>
       </c>
       <c r="E44" t="n">
-        <v>20.40937066078186</v>
+        <v>14.39109349250793</v>
       </c>
       <c r="F44" t="n">
-        <v>13.57011890411377</v>
+        <v>12.82910823822021</v>
       </c>
       <c r="G44" t="n">
-        <v>13.53328895568848</v>
+        <v>12.42289686203003</v>
       </c>
       <c r="H44" t="n">
-        <v>13.96820187568665</v>
+        <v>16.91777610778809</v>
       </c>
       <c r="I44" t="n">
-        <v>12.04555749893188</v>
+        <v>11.5566303730011</v>
       </c>
       <c r="J44" t="n">
-        <v>17.5065815448761</v>
+        <v>12.65830206871033</v>
       </c>
       <c r="K44" t="n">
-        <v>14.14180755615234</v>
+        <v>12.38845825195312</v>
       </c>
       <c r="L44" t="n">
-        <v>15.18100221157074</v>
+        <v>13.56214897632599</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>12.61273741722107</v>
+        <v>10.22365498542786</v>
       </c>
       <c r="C45" t="n">
-        <v>11.42632842063904</v>
+        <v>12.59545373916626</v>
       </c>
       <c r="D45" t="n">
-        <v>10.46914887428284</v>
+        <v>11.17712950706482</v>
       </c>
       <c r="E45" t="n">
-        <v>13.87102484703064</v>
+        <v>10.49653100967407</v>
       </c>
       <c r="F45" t="n">
-        <v>14.54018831253052</v>
+        <v>10.30871486663818</v>
       </c>
       <c r="G45" t="n">
-        <v>13.19382524490356</v>
+        <v>12.52419829368591</v>
       </c>
       <c r="H45" t="n">
-        <v>14.97889256477356</v>
+        <v>11.40162301063538</v>
       </c>
       <c r="I45" t="n">
-        <v>14.23020124435425</v>
+        <v>13.00730657577515</v>
       </c>
       <c r="J45" t="n">
-        <v>11.43975281715393</v>
+        <v>10.75174045562744</v>
       </c>
       <c r="K45" t="n">
-        <v>11.34550046920776</v>
+        <v>14.6741361618042</v>
       </c>
       <c r="L45" t="n">
-        <v>12.81076002120972</v>
+        <v>11.71604886054993</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>15.68746829032898</v>
+        <v>13.24171662330627</v>
       </c>
       <c r="C46" t="n">
-        <v>18.60518980026245</v>
+        <v>12.87471055984497</v>
       </c>
       <c r="D46" t="n">
-        <v>14.55973744392395</v>
+        <v>13.5099413394928</v>
       </c>
       <c r="E46" t="n">
-        <v>13.19265341758728</v>
+        <v>14.88122701644897</v>
       </c>
       <c r="F46" t="n">
-        <v>15.485271692276</v>
+        <v>13.03367924690247</v>
       </c>
       <c r="G46" t="n">
-        <v>12.6648211479187</v>
+        <v>16.94131588935852</v>
       </c>
       <c r="H46" t="n">
-        <v>13.33304905891418</v>
+        <v>12.87150025367737</v>
       </c>
       <c r="I46" t="n">
-        <v>17.6125180721283</v>
+        <v>14.6687023639679</v>
       </c>
       <c r="J46" t="n">
-        <v>15.67369914054871</v>
+        <v>14.92255043983459</v>
       </c>
       <c r="K46" t="n">
-        <v>12.95456957817078</v>
+        <v>13.27929139137268</v>
       </c>
       <c r="L46" t="n">
-        <v>14.97689776420593</v>
+        <v>14.02246351242065</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>18.11292433738708</v>
+        <v>11.6886510848999</v>
       </c>
       <c r="C47" t="n">
-        <v>13.6679675579071</v>
+        <v>10.97797274589539</v>
       </c>
       <c r="D47" t="n">
-        <v>13.08981108665466</v>
+        <v>13.18168449401855</v>
       </c>
       <c r="E47" t="n">
-        <v>16.67621183395386</v>
+        <v>14.61102485656738</v>
       </c>
       <c r="F47" t="n">
-        <v>17.39140558242798</v>
+        <v>18.11675834655762</v>
       </c>
       <c r="G47" t="n">
-        <v>12.30261754989624</v>
+        <v>13.50437378883362</v>
       </c>
       <c r="H47" t="n">
-        <v>17.35053181648254</v>
+        <v>12.76267266273499</v>
       </c>
       <c r="I47" t="n">
-        <v>16.91514539718628</v>
+        <v>17.5153648853302</v>
       </c>
       <c r="J47" t="n">
-        <v>11.88058352470398</v>
+        <v>13.78032994270325</v>
       </c>
       <c r="K47" t="n">
-        <v>12.84763050079346</v>
+        <v>11.82431364059448</v>
       </c>
       <c r="L47" t="n">
-        <v>15.02348291873932</v>
+        <v>13.79631464481354</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>13.94648671150208</v>
+        <v>14.52699875831604</v>
       </c>
       <c r="C48" t="n">
-        <v>17.29094076156616</v>
+        <v>17.13419151306152</v>
       </c>
       <c r="D48" t="n">
-        <v>13.9663553237915</v>
+        <v>11.82203531265259</v>
       </c>
       <c r="E48" t="n">
-        <v>12.58336329460144</v>
+        <v>12.79987335205078</v>
       </c>
       <c r="F48" t="n">
-        <v>13.52769589424133</v>
+        <v>13.40843892097473</v>
       </c>
       <c r="G48" t="n">
-        <v>12.33438014984131</v>
+        <v>15.29010272026062</v>
       </c>
       <c r="H48" t="n">
-        <v>13.25568008422852</v>
+        <v>11.7935733795166</v>
       </c>
       <c r="I48" t="n">
-        <v>12.43785429000854</v>
+        <v>11.77089953422546</v>
       </c>
       <c r="J48" t="n">
-        <v>14.60576701164246</v>
+        <v>13.95762705802917</v>
       </c>
       <c r="K48" t="n">
-        <v>12.40857338905334</v>
+        <v>14.3987877368927</v>
       </c>
       <c r="L48" t="n">
-        <v>13.63570969104767</v>
+        <v>13.69025282859802</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>11.57426452636719</v>
+        <v>13.92702507972717</v>
       </c>
       <c r="C49" t="n">
-        <v>15.27159261703491</v>
+        <v>12.12732553482056</v>
       </c>
       <c r="D49" t="n">
-        <v>15.93751811981201</v>
+        <v>11.64940357208252</v>
       </c>
       <c r="E49" t="n">
-        <v>12.38602709770203</v>
+        <v>11.83096027374268</v>
       </c>
       <c r="F49" t="n">
-        <v>12.38698983192444</v>
+        <v>11.55361175537109</v>
       </c>
       <c r="G49" t="n">
-        <v>16.26201438903809</v>
+        <v>11.3736834526062</v>
       </c>
       <c r="H49" t="n">
-        <v>14.38983964920044</v>
+        <v>11.55882596969604</v>
       </c>
       <c r="I49" t="n">
-        <v>12.78830647468567</v>
+        <v>11.77259302139282</v>
       </c>
       <c r="J49" t="n">
-        <v>12.17321085929871</v>
+        <v>12.12699127197266</v>
       </c>
       <c r="K49" t="n">
-        <v>12.08110761642456</v>
+        <v>12.55669665336609</v>
       </c>
       <c r="L49" t="n">
-        <v>13.5250871181488</v>
+        <v>12.04771165847778</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>12.100421667099</v>
+        <v>14.00222086906433</v>
       </c>
       <c r="C50" t="n">
-        <v>12.62341165542603</v>
+        <v>12.10009717941284</v>
       </c>
       <c r="D50" t="n">
-        <v>12.24189162254333</v>
+        <v>14.37890982627869</v>
       </c>
       <c r="E50" t="n">
-        <v>13.53958058357239</v>
+        <v>11.6076123714447</v>
       </c>
       <c r="F50" t="n">
-        <v>12.31315326690674</v>
+        <v>12.15414714813232</v>
       </c>
       <c r="G50" t="n">
-        <v>12.14552402496338</v>
+        <v>12.26852917671204</v>
       </c>
       <c r="H50" t="n">
-        <v>14.10323309898376</v>
+        <v>15.00353622436523</v>
       </c>
       <c r="I50" t="n">
-        <v>12.51896238327026</v>
+        <v>11.68158984184265</v>
       </c>
       <c r="J50" t="n">
-        <v>14.60339283943176</v>
+        <v>12.35553526878357</v>
       </c>
       <c r="K50" t="n">
-        <v>12.5307891368866</v>
+        <v>11.89542651176453</v>
       </c>
       <c r="L50" t="n">
-        <v>12.87203602790833</v>
+        <v>12.74476044178009</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>11.83162212371826</v>
+        <v>12.20885133743286</v>
       </c>
       <c r="C51" t="n">
-        <v>13.16242218017578</v>
+        <v>10.9075562953949</v>
       </c>
       <c r="D51" t="n">
-        <v>12.06019949913025</v>
+        <v>12.70830726623535</v>
       </c>
       <c r="E51" t="n">
-        <v>12.31330394744873</v>
+        <v>11.65995001792908</v>
       </c>
       <c r="F51" t="n">
-        <v>12.06587362289429</v>
+        <v>11.13003349304199</v>
       </c>
       <c r="G51" t="n">
-        <v>12.4995322227478</v>
+        <v>11.75527429580688</v>
       </c>
       <c r="H51" t="n">
-        <v>12.19052863121033</v>
+        <v>15.06146478652954</v>
       </c>
       <c r="I51" t="n">
-        <v>12.74066352844238</v>
+        <v>11.5784330368042</v>
       </c>
       <c r="J51" t="n">
-        <v>11.69228935241699</v>
+        <v>15.34246873855591</v>
       </c>
       <c r="K51" t="n">
-        <v>12.36857604980469</v>
+        <v>14.35367512702942</v>
       </c>
       <c r="L51" t="n">
-        <v>12.29250111579895</v>
+        <v>12.67060143947601</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.56165749073029</v>
+        <v>13.16927956104279</v>
       </c>
       <c r="C52" t="n">
-        <v>12.60097200393677</v>
+        <v>13.24941926956177</v>
       </c>
       <c r="D52" t="n">
-        <v>12.1963427400589</v>
+        <v>13.09113962650299</v>
       </c>
       <c r="E52" t="n">
-        <v>12.77582414627075</v>
+        <v>13.23499865531921</v>
       </c>
       <c r="F52" t="n">
-        <v>12.70893922805786</v>
+        <v>12.82988420963287</v>
       </c>
       <c r="G52" t="n">
-        <v>12.47972631931305</v>
+        <v>12.96092700004578</v>
       </c>
       <c r="H52" t="n">
-        <v>13.0418172121048</v>
+        <v>13.14575932025909</v>
       </c>
       <c r="I52" t="n">
-        <v>13.20456479549408</v>
+        <v>12.91421369552612</v>
       </c>
       <c r="J52" t="n">
-        <v>12.74156941890717</v>
+        <v>13.23044075489044</v>
       </c>
       <c r="K52" t="n">
-        <v>12.46433500766754</v>
+        <v>13.03086521148682</v>
       </c>
       <c r="L52" t="n">
-        <v>12.67757483625412</v>
+        <v>13.08569273042679</v>
       </c>
     </row>
   </sheetData>
